--- a/research/traditional_assets/database/data/portugal/portugal_transportation.xlsx
+++ b/research/traditional_assets/database/data/portugal/portugal_transportation.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09442278216957514</v>
+        <v>0.09426004432701902</v>
       </c>
       <c r="C2">
-        <v>1316.87855931356</v>
+        <v>1305.010945646429</v>
       </c>
       <c r="D2">
-        <v>1082.97855931356</v>
+        <v>1084.517945646429</v>
       </c>
       <c r="E2">
-        <v>-579.5</v>
+        <v>-566.093</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>13.407</v>
       </c>
       <c r="G2">
         <v>233.9</v>
@@ -1457,28 +1457,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.6743720999999999</v>
       </c>
       <c r="N2">
-        <v>138.2333333333333</v>
+        <v>137.5589612333333</v>
       </c>
       <c r="O2">
-        <v>29.029</v>
+        <v>28.887381859</v>
       </c>
       <c r="P2">
-        <v>109.2043333333333</v>
+        <v>108.6715793743333</v>
       </c>
       <c r="Q2">
-        <v>191.1043333333333</v>
+        <v>190.5715793743333</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09442278216957514</v>
+        <v>0.09481078214850407</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8263921969724817</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>204.9808011531517</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09426004432701902</v>
+        <v>0.09409730648446292</v>
       </c>
       <c r="C3">
-        <v>1305.010945646429</v>
+        <v>1293.147714491677</v>
       </c>
       <c r="D3">
-        <v>1084.517945646429</v>
+        <v>1086.061714491677</v>
       </c>
       <c r="E3">
-        <v>-566.093</v>
+        <v>-552.686</v>
       </c>
       <c r="F3">
-        <v>13.407</v>
+        <v>26.814</v>
       </c>
       <c r="G3">
         <v>233.9</v>
@@ -1539,28 +1539,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M3">
-        <v>0.6743720999999999</v>
+        <v>1.3487442</v>
       </c>
       <c r="N3">
-        <v>137.5589612333333</v>
+        <v>136.8845891333333</v>
       </c>
       <c r="O3">
-        <v>28.887381859</v>
+        <v>28.745763718</v>
       </c>
       <c r="P3">
-        <v>108.6715793743333</v>
+        <v>108.1388254153333</v>
       </c>
       <c r="Q3">
-        <v>190.5715793743333</v>
+        <v>190.0388254153333</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09481078214850407</v>
+        <v>0.09520670049434991</v>
       </c>
       <c r="T3">
-        <v>0.8263921969724817</v>
+        <v>0.8330679490682937</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>204.9808011531517</v>
+        <v>102.4904005765759</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09409730648446292</v>
+        <v>0.0939345686419068</v>
       </c>
       <c r="C4">
-        <v>1293.147714491677</v>
+        <v>1281.288884590987</v>
       </c>
       <c r="D4">
-        <v>1086.061714491677</v>
+        <v>1087.609884590987</v>
       </c>
       <c r="E4">
-        <v>-552.686</v>
+        <v>-539.279</v>
       </c>
       <c r="F4">
-        <v>26.814</v>
+        <v>40.221</v>
       </c>
       <c r="G4">
         <v>233.9</v>
@@ -1621,28 +1621,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M4">
-        <v>1.3487442</v>
+        <v>2.0231163</v>
       </c>
       <c r="N4">
-        <v>136.8845891333333</v>
+        <v>136.2102170333333</v>
       </c>
       <c r="O4">
-        <v>28.745763718</v>
+        <v>28.604145577</v>
       </c>
       <c r="P4">
-        <v>108.1388254153333</v>
+        <v>107.6060714563333</v>
       </c>
       <c r="Q4">
-        <v>190.0388254153333</v>
+        <v>189.5060714563333</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09520670049434991</v>
+        <v>0.09561078210505856</v>
       </c>
       <c r="T4">
-        <v>0.8330679490682937</v>
+        <v>0.8398813455372153</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>102.4904005765759</v>
+        <v>68.32693371771724</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.0939345686419068</v>
+        <v>0.0937718307993507</v>
       </c>
       <c r="C5">
-        <v>1281.288884590987</v>
+        <v>1269.43447479306</v>
       </c>
       <c r="D5">
-        <v>1087.609884590987</v>
+        <v>1089.16247479306</v>
       </c>
       <c r="E5">
-        <v>-539.279</v>
+        <v>-525.872</v>
       </c>
       <c r="F5">
-        <v>40.221</v>
+        <v>53.628</v>
       </c>
       <c r="G5">
         <v>233.9</v>
@@ -1703,28 +1703,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M5">
-        <v>2.0231163</v>
+        <v>2.6974884</v>
       </c>
       <c r="N5">
-        <v>136.2102170333333</v>
+        <v>135.5358449333333</v>
       </c>
       <c r="O5">
-        <v>28.604145577</v>
+        <v>28.462527436</v>
       </c>
       <c r="P5">
-        <v>107.6060714563333</v>
+        <v>107.0733174973333</v>
       </c>
       <c r="Q5">
-        <v>189.5060714563333</v>
+        <v>188.9733174973333</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09561078210505856</v>
+        <v>0.09602328208265698</v>
       </c>
       <c r="T5">
-        <v>0.8398813455372153</v>
+        <v>0.846836687765906</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>68.32693371771724</v>
+        <v>51.24520028828793</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0937718307993507</v>
+        <v>0.09360909295679459</v>
       </c>
       <c r="C6">
-        <v>1269.43447479306</v>
+        <v>1257.584504054375</v>
       </c>
       <c r="D6">
-        <v>1089.16247479306</v>
+        <v>1090.719504054375</v>
       </c>
       <c r="E6">
-        <v>-525.872</v>
+        <v>-512.465</v>
       </c>
       <c r="F6">
-        <v>53.628</v>
+        <v>67.03500000000001</v>
       </c>
       <c r="G6">
         <v>233.9</v>
@@ -1785,28 +1785,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M6">
-        <v>2.6974884</v>
+        <v>3.3718605</v>
       </c>
       <c r="N6">
-        <v>135.5358449333333</v>
+        <v>134.8614728333333</v>
       </c>
       <c r="O6">
-        <v>28.462527436</v>
+        <v>28.320909295</v>
       </c>
       <c r="P6">
-        <v>107.0733174973333</v>
+        <v>106.5405635383333</v>
       </c>
       <c r="Q6">
-        <v>188.9733174973333</v>
+        <v>188.4405635383333</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09602328208265698</v>
+        <v>0.0964444662703101</v>
       </c>
       <c r="T6">
-        <v>0.846836687765906</v>
+        <v>0.853938458252043</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>51.24520028828793</v>
+        <v>40.99616023063033</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09360909295679459</v>
+        <v>0.0934463551142385</v>
       </c>
       <c r="C7">
-        <v>1257.584504054375</v>
+        <v>1245.738991439968</v>
       </c>
       <c r="D7">
-        <v>1090.719504054375</v>
+        <v>1092.280991439968</v>
       </c>
       <c r="E7">
-        <v>-512.465</v>
+        <v>-499.058</v>
       </c>
       <c r="F7">
-        <v>67.03500000000001</v>
+        <v>80.44200000000001</v>
       </c>
       <c r="G7">
         <v>233.9</v>
@@ -1867,28 +1867,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M7">
-        <v>3.3718605</v>
+        <v>4.0462326</v>
       </c>
       <c r="N7">
-        <v>134.8614728333333</v>
+        <v>134.1871007333333</v>
       </c>
       <c r="O7">
-        <v>28.320909295</v>
+        <v>28.179291154</v>
       </c>
       <c r="P7">
-        <v>106.5405635383333</v>
+        <v>106.0078095793333</v>
       </c>
       <c r="Q7">
-        <v>188.4405635383333</v>
+        <v>187.9078095793333</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0964444662703101</v>
+        <v>0.09687461182365797</v>
       </c>
       <c r="T7">
-        <v>0.853938458252043</v>
+        <v>0.8611913302378849</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.99616023063033</v>
+        <v>34.16346685885862</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0934463551142385</v>
+        <v>0.09328361727168238</v>
       </c>
       <c r="C8">
-        <v>1245.738991439968</v>
+        <v>1233.897956124205</v>
       </c>
       <c r="D8">
-        <v>1092.280991439968</v>
+        <v>1093.846956124205</v>
       </c>
       <c r="E8">
-        <v>-499.058</v>
+        <v>-485.651</v>
       </c>
       <c r="F8">
-        <v>80.44199999999999</v>
+        <v>93.84899999999999</v>
       </c>
       <c r="G8">
         <v>233.9</v>
@@ -1949,28 +1949,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M8">
-        <v>4.0462326</v>
+        <v>4.720604699999999</v>
       </c>
       <c r="N8">
-        <v>134.1871007333333</v>
+        <v>133.5127286333333</v>
       </c>
       <c r="O8">
-        <v>28.179291154</v>
+        <v>28.037673013</v>
       </c>
       <c r="P8">
-        <v>106.0078095793333</v>
+        <v>105.4750556203333</v>
       </c>
       <c r="Q8">
-        <v>187.9078095793333</v>
+        <v>187.3750556203333</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09687461182365797</v>
+        <v>0.09731400781901331</v>
       </c>
       <c r="T8">
-        <v>0.8611913302378849</v>
+        <v>0.8686001779653578</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>34.16346685885862</v>
+        <v>29.28297159330739</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09328361727168237</v>
+        <v>0.09312087942912627</v>
       </c>
       <c r="C9">
-        <v>1233.897956124205</v>
+        <v>1222.061417391568</v>
       </c>
       <c r="D9">
-        <v>1093.846956124205</v>
+        <v>1095.417417391568</v>
       </c>
       <c r="E9">
-        <v>-485.651</v>
+        <v>-472.244</v>
       </c>
       <c r="F9">
-        <v>93.84900000000002</v>
+        <v>107.256</v>
       </c>
       <c r="G9">
         <v>233.9</v>
@@ -2031,28 +2031,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M9">
-        <v>4.720604700000001</v>
+        <v>5.394976799999999</v>
       </c>
       <c r="N9">
-        <v>133.5127286333333</v>
+        <v>132.8383565333333</v>
       </c>
       <c r="O9">
-        <v>28.037673013</v>
+        <v>27.896054872</v>
       </c>
       <c r="P9">
-        <v>105.4750556203333</v>
+        <v>104.9423016613333</v>
       </c>
       <c r="Q9">
-        <v>187.3750556203333</v>
+        <v>186.8423016613334</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09731400781901331</v>
+        <v>0.0977629559012242</v>
       </c>
       <c r="T9">
-        <v>0.8686001779653578</v>
+        <v>0.8761700875999496</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.28297159330738</v>
+        <v>25.62260014414396</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09312087942912627</v>
+        <v>0.09295814158657016</v>
       </c>
       <c r="C10">
-        <v>1222.061417391568</v>
+        <v>1210.229394637447</v>
       </c>
       <c r="D10">
-        <v>1095.417417391568</v>
+        <v>1096.992394637447</v>
       </c>
       <c r="E10">
-        <v>-472.244</v>
+        <v>-458.837</v>
       </c>
       <c r="F10">
-        <v>107.256</v>
+        <v>120.663</v>
       </c>
       <c r="G10">
         <v>233.9</v>
@@ -2113,28 +2113,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M10">
-        <v>5.394976799999999</v>
+        <v>6.0693489</v>
       </c>
       <c r="N10">
-        <v>132.8383565333333</v>
+        <v>132.1639844333333</v>
       </c>
       <c r="O10">
-        <v>27.896054872</v>
+        <v>27.754436731</v>
       </c>
       <c r="P10">
-        <v>104.9423016613333</v>
+        <v>104.4095477023333</v>
       </c>
       <c r="Q10">
-        <v>186.8423016613334</v>
+        <v>186.3095477023333</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0977629559012242</v>
+        <v>0.09822177097425291</v>
       </c>
       <c r="T10">
-        <v>0.8761700875999496</v>
+        <v>0.8839063688748622</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.62260014414396</v>
+        <v>22.77564457257241</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09295814158657016</v>
+        <v>0.09279540374401404</v>
       </c>
       <c r="C11">
-        <v>1210.229394637447</v>
+        <v>1198.401907368939</v>
       </c>
       <c r="D11">
-        <v>1096.992394637447</v>
+        <v>1098.571907368938</v>
       </c>
       <c r="E11">
-        <v>-458.837</v>
+        <v>-445.43</v>
       </c>
       <c r="F11">
-        <v>120.663</v>
+        <v>134.07</v>
       </c>
       <c r="G11">
         <v>233.9</v>
@@ -2195,28 +2195,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M11">
-        <v>6.0693489</v>
+        <v>6.743720999999999</v>
       </c>
       <c r="N11">
-        <v>132.1639844333333</v>
+        <v>131.4896123333333</v>
       </c>
       <c r="O11">
-        <v>27.754436731</v>
+        <v>27.61281859</v>
       </c>
       <c r="P11">
-        <v>104.4095477023333</v>
+        <v>103.8767937433333</v>
       </c>
       <c r="Q11">
-        <v>186.3095477023333</v>
+        <v>185.7767937433333</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09822177097425291</v>
+        <v>0.09869078193779339</v>
       </c>
       <c r="T11">
-        <v>0.8839063688748622</v>
+        <v>0.8918145675114395</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.77564457257241</v>
+        <v>20.49808011531517</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09279540374401404</v>
+        <v>0.09263266590145795</v>
       </c>
       <c r="C12">
-        <v>1198.401907368939</v>
+        <v>1186.578975205651</v>
       </c>
       <c r="D12">
-        <v>1098.571907368938</v>
+        <v>1100.155975205651</v>
       </c>
       <c r="E12">
-        <v>-445.4299999999999</v>
+        <v>-432.023</v>
       </c>
       <c r="F12">
-        <v>134.07</v>
+        <v>147.477</v>
       </c>
       <c r="G12">
         <v>233.9</v>
@@ -2277,28 +2277,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M12">
-        <v>6.743721000000001</v>
+        <v>7.4180931</v>
       </c>
       <c r="N12">
-        <v>131.4896123333333</v>
+        <v>130.8152402333333</v>
       </c>
       <c r="O12">
-        <v>27.61281859</v>
+        <v>27.471200449</v>
       </c>
       <c r="P12">
-        <v>103.8767937433333</v>
+        <v>103.3440397843333</v>
       </c>
       <c r="Q12">
-        <v>185.7767937433333</v>
+        <v>185.2440397843333</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09869078193779339</v>
+        <v>0.09917033247354826</v>
       </c>
       <c r="T12">
-        <v>0.8918145675114395</v>
+        <v>0.8999004784769287</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.49808011531517</v>
+        <v>18.63461828665015</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09263266590145795</v>
+        <v>0.09246992805890183</v>
       </c>
       <c r="C13">
-        <v>1186.578975205651</v>
+        <v>1174.760617880519</v>
       </c>
       <c r="D13">
-        <v>1100.155975205651</v>
+        <v>1101.744617880518</v>
       </c>
       <c r="E13">
-        <v>-432.023</v>
+        <v>-418.616</v>
       </c>
       <c r="F13">
-        <v>147.477</v>
+        <v>160.884</v>
       </c>
       <c r="G13">
         <v>233.9</v>
@@ -2359,28 +2359,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M13">
-        <v>7.4180931</v>
+        <v>8.092465199999999</v>
       </c>
       <c r="N13">
-        <v>130.8152402333333</v>
+        <v>130.1408681333333</v>
       </c>
       <c r="O13">
-        <v>27.471200449</v>
+        <v>27.329582308</v>
       </c>
       <c r="P13">
-        <v>103.3440397843333</v>
+        <v>102.8112858253333</v>
       </c>
       <c r="Q13">
-        <v>185.2440397843333</v>
+        <v>184.7112858253333</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09917033247354826</v>
+        <v>0.09966078188511572</v>
       </c>
       <c r="T13">
-        <v>0.8999004784769287</v>
+        <v>0.9081701601461789</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.63461828665015</v>
+        <v>17.08173342942931</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09246992805890183</v>
+        <v>0.09230719021634574</v>
       </c>
       <c r="C14">
-        <v>1174.760617880519</v>
+        <v>1162.946855240615</v>
       </c>
       <c r="D14">
-        <v>1101.744617880518</v>
+        <v>1103.337855240615</v>
       </c>
       <c r="E14">
-        <v>-418.616</v>
+        <v>-405.2089999999999</v>
       </c>
       <c r="F14">
-        <v>160.884</v>
+        <v>174.291</v>
       </c>
       <c r="G14">
         <v>233.9</v>
@@ -2441,28 +2441,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M14">
-        <v>8.092465199999999</v>
+        <v>8.766837300000001</v>
       </c>
       <c r="N14">
-        <v>130.1408681333333</v>
+        <v>129.4664960333333</v>
       </c>
       <c r="O14">
-        <v>27.329582308</v>
+        <v>27.187964167</v>
       </c>
       <c r="P14">
-        <v>102.8112858253333</v>
+        <v>102.2785318663333</v>
       </c>
       <c r="Q14">
-        <v>184.7112858253333</v>
+        <v>184.1785318663333</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09966078188511572</v>
+        <v>0.1001625059957997</v>
       </c>
       <c r="T14">
-        <v>0.9081701601461789</v>
+        <v>0.9166299494400099</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.08173342942931</v>
+        <v>15.76775393485782</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09230719021634574</v>
+        <v>0.09214445237378963</v>
       </c>
       <c r="C15">
-        <v>1162.946855240615</v>
+        <v>1151.137707247988</v>
       </c>
       <c r="D15">
-        <v>1103.337855240615</v>
+        <v>1104.935707247988</v>
       </c>
       <c r="E15">
-        <v>-405.2089999999999</v>
+        <v>-391.802</v>
       </c>
       <c r="F15">
-        <v>174.291</v>
+        <v>187.698</v>
       </c>
       <c r="G15">
         <v>233.9</v>
@@ -2523,28 +2523,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M15">
-        <v>8.766837300000001</v>
+        <v>9.441209400000002</v>
       </c>
       <c r="N15">
-        <v>129.4664960333333</v>
+        <v>128.7921239333333</v>
       </c>
       <c r="O15">
-        <v>27.187964167</v>
+        <v>27.046346026</v>
       </c>
       <c r="P15">
-        <v>102.2785318663333</v>
+        <v>101.7457779073333</v>
       </c>
       <c r="Q15">
-        <v>184.1785318663333</v>
+        <v>183.6457779073334</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1001625059957997</v>
+        <v>0.1006758981090577</v>
       </c>
       <c r="T15">
-        <v>0.9166299494400099</v>
+        <v>0.9252864780197436</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.76775393485782</v>
+        <v>14.64148579665369</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09214445237378963</v>
+        <v>0.09198171453123351</v>
       </c>
       <c r="C16">
-        <v>1151.137707247988</v>
+        <v>1139.333193980487</v>
       </c>
       <c r="D16">
-        <v>1104.935707247988</v>
+        <v>1106.538193980487</v>
       </c>
       <c r="E16">
-        <v>-391.802</v>
+        <v>-378.395</v>
       </c>
       <c r="F16">
-        <v>187.698</v>
+        <v>201.105</v>
       </c>
       <c r="G16">
         <v>233.9</v>
@@ -2605,28 +2605,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M16">
-        <v>9.441209400000002</v>
+        <v>10.1155815</v>
       </c>
       <c r="N16">
-        <v>128.7921239333333</v>
+        <v>128.1177518333333</v>
       </c>
       <c r="O16">
-        <v>27.046346026</v>
+        <v>26.904727885</v>
       </c>
       <c r="P16">
-        <v>101.7457779073333</v>
+        <v>101.2130239483333</v>
       </c>
       <c r="Q16">
-        <v>183.6457779073334</v>
+        <v>183.1130239483333</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1006758981090577</v>
+        <v>0.1012013700367453</v>
       </c>
       <c r="T16">
-        <v>0.9252864780197436</v>
+        <v>0.9341466896248829</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.64148579665369</v>
+        <v>13.66538674354345</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09198171453123351</v>
+        <v>0.0920085766886774</v>
       </c>
       <c r="C17">
-        <v>1139.333193980487</v>
+        <v>1125.661360904511</v>
       </c>
       <c r="D17">
-        <v>1106.538193980487</v>
+        <v>1106.273360904511</v>
       </c>
       <c r="E17">
-        <v>-378.395</v>
+        <v>-364.988</v>
       </c>
       <c r="F17">
-        <v>201.105</v>
+        <v>214.512</v>
       </c>
       <c r="G17">
         <v>233.9</v>
@@ -2687,45 +2687,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M17">
-        <v>10.1155815</v>
+        <v>11.1117216</v>
       </c>
       <c r="N17">
-        <v>128.1177518333333</v>
+        <v>127.1216117333333</v>
       </c>
       <c r="O17">
-        <v>26.904727885</v>
+        <v>26.695538464</v>
       </c>
       <c r="P17">
-        <v>101.2130239483333</v>
+        <v>100.4260732693333</v>
       </c>
       <c r="Q17">
-        <v>183.1130239483333</v>
+        <v>182.3260732693333</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1012013700367453</v>
+        <v>0.1017393532008064</v>
       </c>
       <c r="T17">
-        <v>0.9341466896248829</v>
+        <v>0.9432178586491922</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.21</v>
       </c>
       <c r="W17">
-        <v>0.039737</v>
+        <v>0.040922</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.66538674354345</v>
+        <v>12.44031647925136</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0920085766886774</v>
+        <v>0.09185768884612129</v>
       </c>
       <c r="C18">
-        <v>1125.661360904511</v>
+        <v>1113.743604959164</v>
       </c>
       <c r="D18">
-        <v>1106.273360904511</v>
+        <v>1107.762604959164</v>
       </c>
       <c r="E18">
-        <v>-364.988</v>
+        <v>-351.581</v>
       </c>
       <c r="F18">
-        <v>214.512</v>
+        <v>227.919</v>
       </c>
       <c r="G18">
         <v>233.9</v>
@@ -2769,28 +2769,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M18">
-        <v>11.1117216</v>
+        <v>11.8062042</v>
       </c>
       <c r="N18">
-        <v>127.1216117333333</v>
+        <v>126.4271291333333</v>
       </c>
       <c r="O18">
-        <v>26.695538464</v>
+        <v>26.549697118</v>
       </c>
       <c r="P18">
-        <v>100.4260732693333</v>
+        <v>99.87743201533333</v>
       </c>
       <c r="Q18">
-        <v>182.3260732693333</v>
+        <v>181.7774320153333</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1017393532008064</v>
+        <v>0.102290299814604</v>
       </c>
       <c r="T18">
-        <v>0.9432178586491922</v>
+        <v>0.9525076100596294</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.44031647925136</v>
+        <v>11.70853315694246</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09185768884612129</v>
+        <v>0.09170680100356519</v>
       </c>
       <c r="C19">
-        <v>1113.743604959164</v>
+        <v>1101.829864002485</v>
       </c>
       <c r="D19">
-        <v>1107.762604959164</v>
+        <v>1109.255864002485</v>
       </c>
       <c r="E19">
-        <v>-351.581</v>
+        <v>-338.174</v>
       </c>
       <c r="F19">
-        <v>227.919</v>
+        <v>241.3260000000001</v>
       </c>
       <c r="G19">
         <v>233.9</v>
@@ -2851,28 +2851,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M19">
-        <v>11.8062042</v>
+        <v>12.5006868</v>
       </c>
       <c r="N19">
-        <v>126.4271291333333</v>
+        <v>125.7326465333333</v>
       </c>
       <c r="O19">
-        <v>26.549697118</v>
+        <v>26.403855772</v>
       </c>
       <c r="P19">
-        <v>99.87743201533333</v>
+        <v>99.32879076133332</v>
       </c>
       <c r="Q19">
-        <v>181.7774320153333</v>
+        <v>181.2287907613333</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.102290299814604</v>
+        <v>0.1028546841506893</v>
       </c>
       <c r="T19">
-        <v>0.9525076100596294</v>
+        <v>0.9620239407727601</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.70853315694246</v>
+        <v>11.05805909266788</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09170680100356519</v>
+        <v>0.09155591316100911</v>
       </c>
       <c r="C20">
-        <v>1101.829864002485</v>
+        <v>1089.920154292949</v>
       </c>
       <c r="D20">
-        <v>1109.255864002485</v>
+        <v>1110.753154292949</v>
       </c>
       <c r="E20">
-        <v>-338.174</v>
+        <v>-324.767</v>
       </c>
       <c r="F20">
-        <v>241.326</v>
+        <v>254.733</v>
       </c>
       <c r="G20">
         <v>233.9</v>
@@ -2933,28 +2933,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M20">
-        <v>12.5006868</v>
+        <v>13.1951694</v>
       </c>
       <c r="N20">
-        <v>125.7326465333333</v>
+        <v>125.0381639333333</v>
       </c>
       <c r="O20">
-        <v>26.403855772</v>
+        <v>26.258014426</v>
       </c>
       <c r="P20">
-        <v>99.32879076133332</v>
+        <v>98.78014950733333</v>
       </c>
       <c r="Q20">
-        <v>181.2287907613333</v>
+        <v>180.6801495073333</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1028546841506893</v>
+        <v>0.1034330039024804</v>
       </c>
       <c r="T20">
-        <v>0.9620239407727601</v>
+        <v>0.9717752426146103</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.05805909266788</v>
+        <v>10.47605598252746</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09155591316100911</v>
+        <v>0.09140502531845297</v>
       </c>
       <c r="C21">
-        <v>1089.920154292949</v>
+        <v>1078.014492176936</v>
       </c>
       <c r="D21">
-        <v>1110.753154292949</v>
+        <v>1112.254492176936</v>
       </c>
       <c r="E21">
-        <v>-324.767</v>
+        <v>-311.36</v>
       </c>
       <c r="F21">
-        <v>254.733</v>
+        <v>268.14</v>
       </c>
       <c r="G21">
         <v>233.9</v>
@@ -3015,28 +3015,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M21">
-        <v>13.1951694</v>
+        <v>13.889652</v>
       </c>
       <c r="N21">
-        <v>125.0381639333333</v>
+        <v>124.3436813333333</v>
       </c>
       <c r="O21">
-        <v>26.258014426</v>
+        <v>26.11217308</v>
       </c>
       <c r="P21">
-        <v>98.78014950733333</v>
+        <v>98.23150825333332</v>
       </c>
       <c r="Q21">
-        <v>180.6801495073333</v>
+        <v>180.1315082533333</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1034330039024804</v>
+        <v>0.1040257816480662</v>
       </c>
       <c r="T21">
-        <v>0.9717752426146103</v>
+        <v>0.9817703270025067</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.47605598252746</v>
+        <v>9.952253183401089</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09140502531845297</v>
+        <v>0.09153616747589688</v>
       </c>
       <c r="C22">
-        <v>1078.014492176936</v>
+        <v>1063.302393829453</v>
       </c>
       <c r="D22">
-        <v>1112.254492176936</v>
+        <v>1110.949393829453</v>
       </c>
       <c r="E22">
-        <v>-311.36</v>
+        <v>-297.953</v>
       </c>
       <c r="F22">
-        <v>268.14</v>
+        <v>281.547</v>
       </c>
       <c r="G22">
         <v>233.9</v>
@@ -3097,45 +3097,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M22">
-        <v>13.889652</v>
+        <v>15.0627645</v>
       </c>
       <c r="N22">
-        <v>124.3436813333333</v>
+        <v>123.1705688333333</v>
       </c>
       <c r="O22">
-        <v>26.11217308</v>
+        <v>25.865819455</v>
       </c>
       <c r="P22">
-        <v>98.23150825333332</v>
+        <v>97.30474937833333</v>
       </c>
       <c r="Q22">
-        <v>180.1315082533333</v>
+        <v>179.2047493783333</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1040257816480662</v>
+        <v>0.1046335664251859</v>
       </c>
       <c r="T22">
-        <v>0.9817703270025067</v>
+        <v>0.9920184515014889</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.21</v>
       </c>
       <c r="W22">
-        <v>0.040922</v>
+        <v>0.042265</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.952253183401089</v>
+        <v>9.177155583447734</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09153616747589688</v>
+        <v>0.09139870963334076</v>
       </c>
       <c r="C23">
-        <v>1063.302393829453</v>
+        <v>1051.263421903933</v>
       </c>
       <c r="D23">
-        <v>1110.949393829453</v>
+        <v>1112.317421903933</v>
       </c>
       <c r="E23">
-        <v>-297.953</v>
+        <v>-284.546</v>
       </c>
       <c r="F23">
-        <v>281.547</v>
+        <v>294.954</v>
       </c>
       <c r="G23">
         <v>233.9</v>
@@ -3179,28 +3179,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M23">
-        <v>15.0627645</v>
+        <v>15.780039</v>
       </c>
       <c r="N23">
-        <v>123.1705688333333</v>
+        <v>122.4532943333333</v>
       </c>
       <c r="O23">
-        <v>25.865819455</v>
+        <v>25.71519181</v>
       </c>
       <c r="P23">
-        <v>97.30474937833333</v>
+        <v>96.73810252333332</v>
       </c>
       <c r="Q23">
-        <v>179.2047493783333</v>
+        <v>178.6381025233333</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1046335664251859</v>
+        <v>0.1052569354273599</v>
       </c>
       <c r="T23">
-        <v>0.9920184515014889</v>
+        <v>1.002529348423522</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.177155583447734</v>
+        <v>8.760012147836473</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09139870963334076</v>
+        <v>0.09126125179078466</v>
       </c>
       <c r="C24">
-        <v>1051.263421903933</v>
+        <v>1039.2278233242</v>
       </c>
       <c r="D24">
-        <v>1112.317421903933</v>
+        <v>1113.6888233242</v>
       </c>
       <c r="E24">
-        <v>-284.546</v>
+        <v>-271.139</v>
       </c>
       <c r="F24">
-        <v>294.954</v>
+        <v>308.361</v>
       </c>
       <c r="G24">
         <v>233.9</v>
@@ -3261,28 +3261,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M24">
-        <v>15.780039</v>
+        <v>16.4973135</v>
       </c>
       <c r="N24">
-        <v>122.4532943333333</v>
+        <v>121.7360198333333</v>
       </c>
       <c r="O24">
-        <v>25.71519181</v>
+        <v>25.564564165</v>
       </c>
       <c r="P24">
-        <v>96.73810252333332</v>
+        <v>96.17145566833332</v>
       </c>
       <c r="Q24">
-        <v>178.6381025233333</v>
+        <v>178.0714556683333</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1052569354273599</v>
+        <v>0.1058964958321879</v>
       </c>
       <c r="T24">
-        <v>1.002529348423522</v>
+        <v>1.013313255655218</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.760012147836473</v>
+        <v>8.379142054452279</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09126125179078466</v>
+        <v>0.09112379394822855</v>
       </c>
       <c r="C25">
-        <v>1039.2278233242</v>
+        <v>1027.19561058288</v>
       </c>
       <c r="D25">
-        <v>1113.6888233242</v>
+        <v>1115.06361058288</v>
       </c>
       <c r="E25">
-        <v>-271.139</v>
+        <v>-257.732</v>
       </c>
       <c r="F25">
-        <v>308.361</v>
+        <v>321.768</v>
       </c>
       <c r="G25">
         <v>233.9</v>
@@ -3343,28 +3343,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M25">
-        <v>16.4973135</v>
+        <v>17.214588</v>
       </c>
       <c r="N25">
-        <v>121.7360198333333</v>
+        <v>121.0187453333333</v>
       </c>
       <c r="O25">
-        <v>25.564564165</v>
+        <v>25.41393652</v>
       </c>
       <c r="P25">
-        <v>96.17145566833332</v>
+        <v>95.60480881333332</v>
       </c>
       <c r="Q25">
-        <v>178.0714556683333</v>
+        <v>177.5048088133333</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1058964958321879</v>
+        <v>0.1065528867739849</v>
       </c>
       <c r="T25">
-        <v>1.013313255655218</v>
+        <v>1.024380949919328</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.379142054452279</v>
+        <v>8.030011135516766</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09112379394822855</v>
+        <v>0.09098633610567243</v>
       </c>
       <c r="C26">
-        <v>1027.19561058288</v>
+        <v>1015.166796234362</v>
       </c>
       <c r="D26">
-        <v>1115.06361058288</v>
+        <v>1116.441796234362</v>
       </c>
       <c r="E26">
-        <v>-257.732</v>
+        <v>-244.325</v>
       </c>
       <c r="F26">
-        <v>321.768</v>
+        <v>335.175</v>
       </c>
       <c r="G26">
         <v>233.9</v>
@@ -3425,28 +3425,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M26">
-        <v>17.214588</v>
+        <v>17.9318625</v>
       </c>
       <c r="N26">
-        <v>121.0187453333333</v>
+        <v>120.3014708333333</v>
       </c>
       <c r="O26">
-        <v>25.41393652</v>
+        <v>25.263308875</v>
       </c>
       <c r="P26">
-        <v>95.60480881333334</v>
+        <v>95.03816195833333</v>
       </c>
       <c r="Q26">
-        <v>177.5048088133333</v>
+        <v>176.9381619583334</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1065528867739849</v>
+        <v>0.1072267814742299</v>
       </c>
       <c r="T26">
-        <v>1.024380949919328</v>
+        <v>1.035743782697147</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.030011135516769</v>
+        <v>7.708810690096096</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09098633610567243</v>
+        <v>0.09101319826311632</v>
       </c>
       <c r="C27">
-        <v>1015.166796234362</v>
+        <v>1001.49020196877</v>
       </c>
       <c r="D27">
-        <v>1116.441796234362</v>
+        <v>1116.17220196877</v>
       </c>
       <c r="E27">
-        <v>-244.325</v>
+        <v>-230.9179999999999</v>
       </c>
       <c r="F27">
-        <v>335.175</v>
+        <v>348.5820000000001</v>
       </c>
       <c r="G27">
         <v>233.9</v>
@@ -3507,45 +3507,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M27">
-        <v>17.9318625</v>
+        <v>18.9280026</v>
       </c>
       <c r="N27">
-        <v>120.3014708333333</v>
+        <v>119.3053307333333</v>
       </c>
       <c r="O27">
-        <v>25.263308875</v>
+        <v>25.05411945399999</v>
       </c>
       <c r="P27">
-        <v>95.03816195833333</v>
+        <v>94.25121127933332</v>
       </c>
       <c r="Q27">
-        <v>176.9381619583334</v>
+        <v>176.1512112793333</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1072267814742299</v>
+        <v>0.1079188895447518</v>
       </c>
       <c r="T27">
-        <v>1.035743782697147</v>
+        <v>1.047413719063556</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.21</v>
       </c>
       <c r="W27">
-        <v>0.042265</v>
+        <v>0.042897</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.708810690096096</v>
+        <v>7.303112549938751</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09101319826311632</v>
+        <v>0.09088206042056023</v>
       </c>
       <c r="C28">
-        <v>1001.49020196877</v>
+        <v>989.4005641264662</v>
       </c>
       <c r="D28">
-        <v>1116.17220196877</v>
+        <v>1117.489564126466</v>
       </c>
       <c r="E28">
-        <v>-230.9179999999999</v>
+        <v>-217.511</v>
       </c>
       <c r="F28">
-        <v>348.5820000000001</v>
+        <v>361.989</v>
       </c>
       <c r="G28">
         <v>233.9</v>
@@ -3589,28 +3589,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M28">
-        <v>18.9280026</v>
+        <v>19.6560027</v>
       </c>
       <c r="N28">
-        <v>119.3053307333333</v>
+        <v>118.5773306333333</v>
       </c>
       <c r="O28">
-        <v>25.05411945399999</v>
+        <v>24.901239433</v>
       </c>
       <c r="P28">
-        <v>94.25121127933332</v>
+        <v>93.67609120033332</v>
       </c>
       <c r="Q28">
-        <v>176.1512112793333</v>
+        <v>175.5760912003333</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1079188895447518</v>
+        <v>0.1086299594802195</v>
       </c>
       <c r="T28">
-        <v>1.047413719063556</v>
+        <v>1.059403379713975</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.303112549938751</v>
+        <v>7.032626899941019</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09088206042056023</v>
+        <v>0.09075092257800411</v>
       </c>
       <c r="C29">
-        <v>989.4005641264662</v>
+        <v>977.3140395918193</v>
       </c>
       <c r="D29">
-        <v>1117.489564126466</v>
+        <v>1118.810039591819</v>
       </c>
       <c r="E29">
-        <v>-217.511</v>
+        <v>-204.1039999999999</v>
       </c>
       <c r="F29">
-        <v>361.989</v>
+        <v>375.3960000000001</v>
       </c>
       <c r="G29">
         <v>233.9</v>
@@ -3671,28 +3671,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M29">
-        <v>19.6560027</v>
+        <v>20.3840028</v>
       </c>
       <c r="N29">
-        <v>118.5773306333333</v>
+        <v>117.8493305333333</v>
       </c>
       <c r="O29">
-        <v>24.901239433</v>
+        <v>24.748359412</v>
       </c>
       <c r="P29">
-        <v>93.67609120033332</v>
+        <v>93.10097112133332</v>
       </c>
       <c r="Q29">
-        <v>175.5760912003333</v>
+        <v>175.0009711213333</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1086299594802195</v>
+        <v>0.109360781358339</v>
       </c>
       <c r="T29">
-        <v>1.059403379713975</v>
+        <v>1.071726086493574</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.032626899941019</v>
+        <v>6.781461653514554</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09075092257800411</v>
+        <v>0.09061978473544802</v>
       </c>
       <c r="C30">
-        <v>977.3140395918193</v>
+        <v>965.230639414355</v>
       </c>
       <c r="D30">
-        <v>1118.810039591819</v>
+        <v>1120.133639414355</v>
       </c>
       <c r="E30">
-        <v>-204.1039999999999</v>
+        <v>-190.6969999999999</v>
       </c>
       <c r="F30">
-        <v>375.3960000000001</v>
+        <v>388.8030000000001</v>
       </c>
       <c r="G30">
         <v>233.9</v>
@@ -3753,28 +3753,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M30">
-        <v>20.3840028</v>
+        <v>21.1120029</v>
       </c>
       <c r="N30">
-        <v>117.8493305333333</v>
+        <v>117.1213304333333</v>
       </c>
       <c r="O30">
-        <v>24.748359412</v>
+        <v>24.59547939099999</v>
       </c>
       <c r="P30">
-        <v>93.10097112133332</v>
+        <v>92.52585104233331</v>
       </c>
       <c r="Q30">
-        <v>175.0009711213333</v>
+        <v>174.4258510423333</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.109360781358339</v>
+        <v>0.1101121897682366</v>
       </c>
       <c r="T30">
-        <v>1.071726086493574</v>
+        <v>1.084395911774006</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.781461653514554</v>
+        <v>6.547618148220948</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09061978473544802</v>
+        <v>0.09048864689289191</v>
       </c>
       <c r="C31">
-        <v>965.2306394143551</v>
+        <v>953.1503746959495</v>
       </c>
       <c r="D31">
-        <v>1120.133639414355</v>
+        <v>1121.460374695949</v>
       </c>
       <c r="E31">
-        <v>-190.697</v>
+        <v>-177.29</v>
       </c>
       <c r="F31">
-        <v>388.803</v>
+        <v>402.21</v>
       </c>
       <c r="G31">
         <v>233.9</v>
@@ -3835,28 +3835,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M31">
-        <v>21.1120029</v>
+        <v>21.840003</v>
       </c>
       <c r="N31">
-        <v>117.1213304333333</v>
+        <v>116.3933303333333</v>
       </c>
       <c r="O31">
-        <v>24.595479391</v>
+        <v>24.44259937</v>
       </c>
       <c r="P31">
-        <v>92.52585104233333</v>
+        <v>91.95073096333333</v>
       </c>
       <c r="Q31">
-        <v>174.4258510423333</v>
+        <v>173.8507309633333</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1101121897682366</v>
+        <v>0.1108850669898456</v>
       </c>
       <c r="T31">
-        <v>1.084395911774006</v>
+        <v>1.09742773206245</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.54761814822095</v>
+        <v>6.329364209946919</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09048864689289191</v>
+        <v>0.09035750905033579</v>
       </c>
       <c r="C32">
-        <v>953.1503746959495</v>
+        <v>941.0732565911392</v>
       </c>
       <c r="D32">
-        <v>1121.460374695949</v>
+        <v>1122.790256591139</v>
       </c>
       <c r="E32">
-        <v>-177.29</v>
+        <v>-163.883</v>
       </c>
       <c r="F32">
-        <v>402.21</v>
+        <v>415.617</v>
       </c>
       <c r="G32">
         <v>233.9</v>
@@ -3917,28 +3917,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M32">
-        <v>21.840003</v>
+        <v>22.5680031</v>
       </c>
       <c r="N32">
-        <v>116.3933303333333</v>
+        <v>115.6653302333333</v>
       </c>
       <c r="O32">
-        <v>24.44259937</v>
+        <v>24.28971934899999</v>
       </c>
       <c r="P32">
-        <v>91.95073096333333</v>
+        <v>91.37561088433333</v>
       </c>
       <c r="Q32">
-        <v>173.8507309633333</v>
+        <v>173.2756108843333</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1108850669898456</v>
+        <v>0.111680346449762</v>
       </c>
       <c r="T32">
-        <v>1.09742773206245</v>
+        <v>1.110837286272299</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.329364209946919</v>
+        <v>6.125191170916372</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09035750905033579</v>
+        <v>0.09047917120777969</v>
       </c>
       <c r="C33">
-        <v>941.0732565911392</v>
+        <v>926.4323629578304</v>
       </c>
       <c r="D33">
-        <v>1122.790256591139</v>
+        <v>1121.55636295783</v>
       </c>
       <c r="E33">
-        <v>-163.883</v>
+        <v>-150.476</v>
       </c>
       <c r="F33">
-        <v>415.617</v>
+        <v>429.024</v>
       </c>
       <c r="G33">
         <v>233.9</v>
@@ -3999,45 +3999,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M33">
-        <v>22.5680031</v>
+        <v>23.7250272</v>
       </c>
       <c r="N33">
-        <v>115.6653302333333</v>
+        <v>114.5083061333333</v>
       </c>
       <c r="O33">
-        <v>24.28971934899999</v>
+        <v>24.046744288</v>
       </c>
       <c r="P33">
-        <v>91.37561088433333</v>
+        <v>90.46156184533332</v>
       </c>
       <c r="Q33">
-        <v>173.2756108843333</v>
+        <v>172.3615618453333</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.111680346449762</v>
+        <v>0.112499016482029</v>
       </c>
       <c r="T33">
-        <v>1.110837286272299</v>
+        <v>1.124641239135378</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.21</v>
       </c>
       <c r="W33">
-        <v>0.042897</v>
+        <v>0.043687</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>6.125191170916372</v>
+        <v>5.82647733838355</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09047917120777969</v>
+        <v>0.09035593336522357</v>
       </c>
       <c r="C34">
-        <v>926.4323629578304</v>
+        <v>914.2752549473062</v>
       </c>
       <c r="D34">
-        <v>1121.55636295783</v>
+        <v>1122.806254947306</v>
       </c>
       <c r="E34">
-        <v>-150.476</v>
+        <v>-137.069</v>
       </c>
       <c r="F34">
-        <v>429.024</v>
+        <v>442.431</v>
       </c>
       <c r="G34">
         <v>233.9</v>
@@ -4081,28 +4081,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M34">
-        <v>23.7250272</v>
+        <v>24.4664343</v>
       </c>
       <c r="N34">
-        <v>114.5083061333333</v>
+        <v>113.7668990333333</v>
       </c>
       <c r="O34">
-        <v>24.046744288</v>
+        <v>23.891048797</v>
       </c>
       <c r="P34">
-        <v>90.46156184533332</v>
+        <v>89.87585023633332</v>
       </c>
       <c r="Q34">
-        <v>172.3615618453333</v>
+        <v>171.7758502363333</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.112499016482029</v>
+        <v>0.1133421244257068</v>
       </c>
       <c r="T34">
-        <v>1.124641239135378</v>
+        <v>1.138857250292878</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.82647733838355</v>
+        <v>5.649917419038593</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09035593336522357</v>
+        <v>0.09023269552266748</v>
       </c>
       <c r="C35">
-        <v>914.2752549473062</v>
+        <v>902.1209358700348</v>
       </c>
       <c r="D35">
-        <v>1122.806254947306</v>
+        <v>1124.058935870035</v>
       </c>
       <c r="E35">
-        <v>-137.069</v>
+        <v>-123.662</v>
       </c>
       <c r="F35">
-        <v>442.431</v>
+        <v>455.838</v>
       </c>
       <c r="G35">
         <v>233.9</v>
@@ -4163,28 +4163,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M35">
-        <v>24.4664343</v>
+        <v>25.2078414</v>
       </c>
       <c r="N35">
-        <v>113.7668990333333</v>
+        <v>113.0254919333333</v>
       </c>
       <c r="O35">
-        <v>23.891048797</v>
+        <v>23.73535330599999</v>
       </c>
       <c r="P35">
-        <v>89.87585023633332</v>
+        <v>89.29013862733332</v>
       </c>
       <c r="Q35">
-        <v>171.7758502363333</v>
+        <v>171.1901386273333</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1133421244257068</v>
+        <v>0.1142107810949507</v>
       </c>
       <c r="T35">
-        <v>1.138857250292878</v>
+        <v>1.153504049667271</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.649917419038593</v>
+        <v>5.483743377302163</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09023269552266748</v>
+        <v>0.09010945768011135</v>
       </c>
       <c r="C36">
-        <v>902.1209358700348</v>
+        <v>889.9694150710282</v>
       </c>
       <c r="D36">
-        <v>1124.058935870035</v>
+        <v>1125.314415071028</v>
       </c>
       <c r="E36">
-        <v>-123.662</v>
+        <v>-110.2549999999999</v>
       </c>
       <c r="F36">
-        <v>455.838</v>
+        <v>469.2450000000001</v>
       </c>
       <c r="G36">
         <v>233.9</v>
@@ -4245,28 +4245,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M36">
-        <v>25.2078414</v>
+        <v>25.9492485</v>
       </c>
       <c r="N36">
-        <v>113.0254919333333</v>
+        <v>112.2840848333333</v>
       </c>
       <c r="O36">
-        <v>23.73535330599999</v>
+        <v>23.57965781499999</v>
       </c>
       <c r="P36">
-        <v>89.29013862733332</v>
+        <v>88.70442701833332</v>
       </c>
       <c r="Q36">
-        <v>171.1901386273333</v>
+        <v>170.6044270183333</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1142107810949507</v>
+        <v>0.1151061656617098</v>
       </c>
       <c r="T36">
-        <v>1.153504049667271</v>
+        <v>1.168601519791646</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.483743377302163</v>
+        <v>5.32706499509353</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09010945768011135</v>
+        <v>0.08998621983755525</v>
       </c>
       <c r="C37">
-        <v>889.9694150710282</v>
+        <v>877.8207019370932</v>
       </c>
       <c r="D37">
-        <v>1125.314415071028</v>
+        <v>1126.572701937093</v>
       </c>
       <c r="E37">
-        <v>-110.2549999999999</v>
+        <v>-96.8479999999999</v>
       </c>
       <c r="F37">
-        <v>469.2450000000001</v>
+        <v>482.6520000000001</v>
       </c>
       <c r="G37">
         <v>233.9</v>
@@ -4327,28 +4327,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M37">
-        <v>25.9492485</v>
+        <v>26.69065560000001</v>
       </c>
       <c r="N37">
-        <v>112.2840848333333</v>
+        <v>111.5426777333333</v>
       </c>
       <c r="O37">
-        <v>23.57965781499999</v>
+        <v>23.42396232399999</v>
       </c>
       <c r="P37">
-        <v>88.70442701833332</v>
+        <v>88.1187154093333</v>
       </c>
       <c r="Q37">
-        <v>170.6044270183333</v>
+        <v>170.0187154093333</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1151061656617098</v>
+        <v>0.1160295309961801</v>
       </c>
       <c r="T37">
-        <v>1.168601519791646</v>
+        <v>1.184170785857408</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.32706499509353</v>
+        <v>5.179090967452042</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08998621983755525</v>
+        <v>0.08986298199499915</v>
       </c>
       <c r="C38">
-        <v>877.8207019370932</v>
+        <v>865.6748058970697</v>
       </c>
       <c r="D38">
-        <v>1126.572701937093</v>
+        <v>1127.83380589707</v>
       </c>
       <c r="E38">
-        <v>-96.84800000000001</v>
+        <v>-83.44099999999997</v>
       </c>
       <c r="F38">
-        <v>482.652</v>
+        <v>496.059</v>
       </c>
       <c r="G38">
         <v>233.9</v>
@@ -4409,28 +4409,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M38">
-        <v>26.6906556</v>
+        <v>27.4320627</v>
       </c>
       <c r="N38">
-        <v>111.5426777333333</v>
+        <v>110.8012706333333</v>
       </c>
       <c r="O38">
-        <v>23.423962324</v>
+        <v>23.26826683299999</v>
       </c>
       <c r="P38">
-        <v>88.11871540933332</v>
+        <v>87.53300380033332</v>
       </c>
       <c r="Q38">
-        <v>170.0187154093333</v>
+        <v>169.4330038003333</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1160295309961801</v>
+        <v>0.1169822095158717</v>
       </c>
       <c r="T38">
-        <v>1.184170785857408</v>
+        <v>1.200234314337955</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.179090967452044</v>
+        <v>5.039115535899286</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08986298199499915</v>
+        <v>0.08973974415244304</v>
       </c>
       <c r="C39">
-        <v>865.6748058970697</v>
+        <v>853.5317364220629</v>
       </c>
       <c r="D39">
-        <v>1127.83380589707</v>
+        <v>1129.097736422063</v>
       </c>
       <c r="E39">
-        <v>-83.44099999999997</v>
+        <v>-70.03399999999999</v>
       </c>
       <c r="F39">
-        <v>496.059</v>
+        <v>509.466</v>
       </c>
       <c r="G39">
         <v>233.9</v>
@@ -4491,28 +4491,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M39">
-        <v>27.4320627</v>
+        <v>28.1734698</v>
       </c>
       <c r="N39">
-        <v>110.8012706333333</v>
+        <v>110.0598635333333</v>
       </c>
       <c r="O39">
-        <v>23.26826683299999</v>
+        <v>23.112571342</v>
       </c>
       <c r="P39">
-        <v>87.53300380033332</v>
+        <v>86.94729219133332</v>
       </c>
       <c r="Q39">
-        <v>169.4330038003333</v>
+        <v>168.8472921913333</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1169822095158717</v>
+        <v>0.1179656196007146</v>
       </c>
       <c r="T39">
-        <v>1.200234314337955</v>
+        <v>1.216816021156585</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.039115535899286</v>
+        <v>4.906507232322989</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08973974415244304</v>
+        <v>0.08961650630988693</v>
       </c>
       <c r="C40">
-        <v>853.5317364220629</v>
+        <v>841.3915030256819</v>
       </c>
       <c r="D40">
-        <v>1129.097736422063</v>
+        <v>1130.364503025682</v>
       </c>
       <c r="E40">
-        <v>-70.03399999999999</v>
+        <v>-56.62699999999995</v>
       </c>
       <c r="F40">
-        <v>509.466</v>
+        <v>522.873</v>
       </c>
       <c r="G40">
         <v>233.9</v>
@@ -4573,28 +4573,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M40">
-        <v>28.1734698</v>
+        <v>28.9148769</v>
       </c>
       <c r="N40">
-        <v>110.0598635333333</v>
+        <v>109.3184564333333</v>
       </c>
       <c r="O40">
-        <v>23.112571342</v>
+        <v>22.956875851</v>
       </c>
       <c r="P40">
-        <v>86.94729219133332</v>
+        <v>86.36158058233333</v>
       </c>
       <c r="Q40">
-        <v>168.8472921913333</v>
+        <v>168.2615805823334</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1179656196007146</v>
+        <v>0.1189812726391589</v>
       </c>
       <c r="T40">
-        <v>1.216816021156585</v>
+        <v>1.233941390493859</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.906507232322989</v>
+        <v>4.780699354571118</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08961650630988693</v>
+        <v>0.08949326846733083</v>
       </c>
       <c r="C41">
-        <v>841.3915030256819</v>
+        <v>829.2541152642781</v>
       </c>
       <c r="D41">
-        <v>1130.364503025682</v>
+        <v>1131.634115264278</v>
       </c>
       <c r="E41">
-        <v>-56.62699999999995</v>
+        <v>-43.21999999999991</v>
       </c>
       <c r="F41">
-        <v>522.873</v>
+        <v>536.2800000000001</v>
       </c>
       <c r="G41">
         <v>233.9</v>
@@ -4655,28 +4655,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M41">
-        <v>28.9148769</v>
+        <v>29.65628400000001</v>
       </c>
       <c r="N41">
-        <v>109.3184564333333</v>
+        <v>108.5770493333333</v>
       </c>
       <c r="O41">
-        <v>22.956875851</v>
+        <v>22.80118036</v>
       </c>
       <c r="P41">
-        <v>86.36158058233333</v>
+        <v>85.77586897333333</v>
       </c>
       <c r="Q41">
-        <v>168.2615805823334</v>
+        <v>167.6758689733333</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1189812726391589</v>
+        <v>0.1200307807788847</v>
       </c>
       <c r="T41">
-        <v>1.233941390493859</v>
+        <v>1.251637605475708</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.780699354571118</v>
+        <v>4.661181870706839</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08949326846733083</v>
+        <v>0.08937003062477471</v>
       </c>
       <c r="C42">
-        <v>829.2541152642781</v>
+        <v>817.1195827371856</v>
       </c>
       <c r="D42">
-        <v>1131.634115264278</v>
+        <v>1132.906582737186</v>
       </c>
       <c r="E42">
-        <v>-43.21999999999991</v>
+        <v>-29.81299999999999</v>
       </c>
       <c r="F42">
-        <v>536.2800000000001</v>
+        <v>549.687</v>
       </c>
       <c r="G42">
         <v>233.9</v>
@@ -4737,28 +4737,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M42">
-        <v>29.65628400000001</v>
+        <v>30.3976911</v>
       </c>
       <c r="N42">
-        <v>108.5770493333333</v>
+        <v>107.8356422333333</v>
       </c>
       <c r="O42">
-        <v>22.80118036</v>
+        <v>22.645484869</v>
       </c>
       <c r="P42">
-        <v>85.77586897333333</v>
+        <v>85.19015736433332</v>
       </c>
       <c r="Q42">
-        <v>167.6758689733333</v>
+        <v>167.0901573643333</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1200307807788847</v>
+        <v>0.1211158654657198</v>
       </c>
       <c r="T42">
-        <v>1.251637605475708</v>
+        <v>1.269933692151857</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.661181870706839</v>
+        <v>4.547494508006673</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08937003062477471</v>
+        <v>0.09007629278221861</v>
       </c>
       <c r="C43">
-        <v>817.1195827371856</v>
+        <v>796.4587598335263</v>
       </c>
       <c r="D43">
-        <v>1132.906582737186</v>
+        <v>1125.652759833526</v>
       </c>
       <c r="E43">
-        <v>-29.81299999999999</v>
+        <v>-16.40599999999995</v>
       </c>
       <c r="F43">
-        <v>549.687</v>
+        <v>563.0940000000001</v>
       </c>
       <c r="G43">
         <v>233.9</v>
@@ -4819,45 +4819,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M43">
-        <v>30.3976911</v>
+        <v>32.5468332</v>
       </c>
       <c r="N43">
-        <v>107.8356422333333</v>
+        <v>105.6865001333333</v>
       </c>
       <c r="O43">
-        <v>22.645484869</v>
+        <v>22.19416502799999</v>
       </c>
       <c r="P43">
-        <v>85.19015736433332</v>
+        <v>83.49233510533332</v>
       </c>
       <c r="Q43">
-        <v>167.0901573643333</v>
+        <v>165.3923351053333</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1211158654657198</v>
+        <v>0.1222383668658941</v>
       </c>
       <c r="T43">
-        <v>1.269933692151857</v>
+        <v>1.288860678368563</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.21</v>
       </c>
       <c r="W43">
-        <v>0.043687</v>
+        <v>0.04566200000000001</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.547494508006673</v>
+        <v>4.247213007910499</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09007629278221863</v>
+        <v>0.0899728049396625</v>
       </c>
       <c r="C44">
-        <v>796.4587598335263</v>
+        <v>784.1088409924159</v>
       </c>
       <c r="D44">
-        <v>1125.652759833526</v>
+        <v>1126.709840992416</v>
       </c>
       <c r="E44">
-        <v>-16.40599999999995</v>
+        <v>-2.999000000000024</v>
       </c>
       <c r="F44">
-        <v>563.0940000000001</v>
+        <v>576.501</v>
       </c>
       <c r="G44">
         <v>233.9</v>
@@ -4901,28 +4901,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M44">
-        <v>32.5468332</v>
+        <v>33.3217578</v>
       </c>
       <c r="N44">
-        <v>105.6865001333333</v>
+        <v>104.9115755333333</v>
       </c>
       <c r="O44">
-        <v>22.19416502799999</v>
+        <v>22.031430862</v>
       </c>
       <c r="P44">
-        <v>83.49233510533332</v>
+        <v>82.88014467133333</v>
       </c>
       <c r="Q44">
-        <v>165.3923351053333</v>
+        <v>164.7801446713333</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1222383668658941</v>
+        <v>0.1234002542801096</v>
       </c>
       <c r="T44">
-        <v>1.288860678368563</v>
+        <v>1.308451769364803</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.247213007910499</v>
+        <v>4.148440612377698</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0899728049396625</v>
+        <v>0.0898693170971064</v>
       </c>
       <c r="C45">
-        <v>784.1088409924159</v>
+        <v>771.7609093909822</v>
       </c>
       <c r="D45">
-        <v>1126.709840992416</v>
+        <v>1127.768909390982</v>
       </c>
       <c r="E45">
-        <v>-2.999000000000024</v>
+        <v>10.40800000000002</v>
       </c>
       <c r="F45">
-        <v>576.501</v>
+        <v>589.908</v>
       </c>
       <c r="G45">
         <v>233.9</v>
@@ -4983,28 +4983,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M45">
-        <v>33.3217578</v>
+        <v>34.09668240000001</v>
       </c>
       <c r="N45">
-        <v>104.9115755333333</v>
+        <v>104.1366509333333</v>
       </c>
       <c r="O45">
-        <v>22.031430862</v>
+        <v>21.86869669599999</v>
       </c>
       <c r="P45">
-        <v>82.88014467133333</v>
+        <v>82.26795423733333</v>
       </c>
       <c r="Q45">
-        <v>164.7801446713333</v>
+        <v>164.1679542373333</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1234002542801096</v>
+        <v>0.1246036376734043</v>
       </c>
       <c r="T45">
-        <v>1.308451769364803</v>
+        <v>1.328742542182337</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.148440612377698</v>
+        <v>4.054157871187295</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.0898693170971064</v>
+        <v>0.09101007925455029</v>
       </c>
       <c r="C46">
-        <v>771.7609093909822</v>
+        <v>746.7884983137274</v>
       </c>
       <c r="D46">
-        <v>1127.768909390982</v>
+        <v>1116.203498313727</v>
       </c>
       <c r="E46">
-        <v>10.40800000000002</v>
+        <v>23.81500000000005</v>
       </c>
       <c r="F46">
-        <v>589.908</v>
+        <v>603.3150000000001</v>
       </c>
       <c r="G46">
         <v>233.9</v>
@@ -5065,45 +5065,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M46">
-        <v>34.09668240000001</v>
+        <v>36.9832095</v>
       </c>
       <c r="N46">
-        <v>104.1366509333333</v>
+        <v>101.2501238333333</v>
       </c>
       <c r="O46">
-        <v>21.86869669599999</v>
+        <v>21.26252600499999</v>
       </c>
       <c r="P46">
-        <v>82.26795423733333</v>
+        <v>79.98759782833332</v>
       </c>
       <c r="Q46">
-        <v>164.1679542373333</v>
+        <v>161.8875978283333</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1246036376734043</v>
+        <v>0.1258507804628187</v>
       </c>
       <c r="T46">
-        <v>1.328742542182337</v>
+        <v>1.349771161284145</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.21</v>
       </c>
       <c r="W46">
-        <v>0.04566200000000001</v>
+        <v>0.048427</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.054157871187295</v>
+        <v>3.737732208810415</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09101007925455029</v>
+        <v>0.09093424141199419</v>
       </c>
       <c r="C47">
-        <v>746.7884983137274</v>
+        <v>734.1430009040952</v>
       </c>
       <c r="D47">
-        <v>1116.203498313727</v>
+        <v>1116.965000904095</v>
       </c>
       <c r="E47">
-        <v>23.81500000000005</v>
+        <v>37.22200000000009</v>
       </c>
       <c r="F47">
-        <v>603.3150000000001</v>
+        <v>616.7220000000001</v>
       </c>
       <c r="G47">
         <v>233.9</v>
@@ -5147,28 +5147,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M47">
-        <v>36.9832095</v>
+        <v>37.8050586</v>
       </c>
       <c r="N47">
-        <v>101.2501238333333</v>
+        <v>100.4282747333333</v>
       </c>
       <c r="O47">
-        <v>21.26252600499999</v>
+        <v>21.089937694</v>
       </c>
       <c r="P47">
-        <v>79.98759782833332</v>
+        <v>79.33833703933333</v>
       </c>
       <c r="Q47">
-        <v>161.8875978283333</v>
+        <v>161.2383370393333</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1258507804628187</v>
+        <v>0.1271441137259151</v>
       </c>
       <c r="T47">
-        <v>1.349771161284145</v>
+        <v>1.371578618130464</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.737732208810415</v>
+        <v>3.656477160792797</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09093424141199419</v>
+        <v>0.09085840356943807</v>
       </c>
       <c r="C48">
-        <v>734.1430009040952</v>
+        <v>721.4985432369107</v>
       </c>
       <c r="D48">
-        <v>1116.965000904095</v>
+        <v>1117.727543236911</v>
       </c>
       <c r="E48">
-        <v>37.22200000000009</v>
+        <v>50.62900000000002</v>
       </c>
       <c r="F48">
-        <v>616.7220000000001</v>
+        <v>630.129</v>
       </c>
       <c r="G48">
         <v>233.9</v>
@@ -5229,28 +5229,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M48">
-        <v>37.8050586</v>
+        <v>38.6269077</v>
       </c>
       <c r="N48">
-        <v>100.4282747333333</v>
+        <v>99.60642563333332</v>
       </c>
       <c r="O48">
-        <v>21.089937694</v>
+        <v>20.91734938299999</v>
       </c>
       <c r="P48">
-        <v>79.33833703933333</v>
+        <v>78.68907625033333</v>
       </c>
       <c r="Q48">
-        <v>161.2383370393333</v>
+        <v>160.5890762503333</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1271441137259151</v>
+        <v>0.1284862520178077</v>
       </c>
       <c r="T48">
-        <v>1.371578618130464</v>
+        <v>1.394208997876644</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.656477160792797</v>
+        <v>3.57867977439295</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09085840356943807</v>
+        <v>0.09078256572688197</v>
       </c>
       <c r="C49">
-        <v>721.4985432369107</v>
+        <v>708.855127443097</v>
       </c>
       <c r="D49">
-        <v>1117.727543236911</v>
+        <v>1118.491127443097</v>
       </c>
       <c r="E49">
-        <v>50.62900000000002</v>
+        <v>64.03600000000006</v>
       </c>
       <c r="F49">
-        <v>630.129</v>
+        <v>643.5360000000001</v>
       </c>
       <c r="G49">
         <v>233.9</v>
@@ -5311,28 +5311,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M49">
-        <v>38.6269077</v>
+        <v>39.44875680000001</v>
       </c>
       <c r="N49">
-        <v>99.60642563333332</v>
+        <v>98.78457653333331</v>
       </c>
       <c r="O49">
-        <v>20.91734938299999</v>
+        <v>20.74476107199999</v>
       </c>
       <c r="P49">
-        <v>78.68907625033333</v>
+        <v>78.03981546133332</v>
       </c>
       <c r="Q49">
-        <v>160.5890762503333</v>
+        <v>159.9398154613333</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1284862520178077</v>
+        <v>0.1298800110132345</v>
       </c>
       <c r="T49">
-        <v>1.394208997876644</v>
+        <v>1.417709776843832</v>
       </c>
       <c r="U49">
         <v>0.0613</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.57867977439295</v>
+        <v>3.504123945759763</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09078256572688195</v>
+        <v>0.09179060788432584</v>
       </c>
       <c r="C50">
-        <v>708.8551274430973</v>
+        <v>685.3829739190865</v>
       </c>
       <c r="D50">
-        <v>1118.491127443097</v>
+        <v>1108.425973919086</v>
       </c>
       <c r="E50">
-        <v>64.03599999999994</v>
+        <v>77.44299999999998</v>
       </c>
       <c r="F50">
-        <v>643.5359999999999</v>
+        <v>656.943</v>
       </c>
       <c r="G50">
         <v>233.9</v>
@@ -5393,45 +5393,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M50">
-        <v>39.4487568</v>
+        <v>42.1100463</v>
       </c>
       <c r="N50">
-        <v>98.78457653333332</v>
+        <v>96.12328703333333</v>
       </c>
       <c r="O50">
-        <v>20.744761072</v>
+        <v>20.185890277</v>
       </c>
       <c r="P50">
-        <v>78.03981546133332</v>
+        <v>75.93739675633333</v>
       </c>
       <c r="Q50">
-        <v>159.9398154613333</v>
+        <v>157.8373967563333</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1298800110132345</v>
+        <v>0.1313284272241683</v>
       </c>
       <c r="T50">
-        <v>1.417709776843832</v>
+        <v>1.442132154986203</v>
       </c>
       <c r="U50">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V50">
         <v>0.21</v>
       </c>
       <c r="W50">
-        <v>0.048427</v>
+        <v>0.050639</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y50">
-        <v>3.504123945759764</v>
+        <v>3.282668756726903</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09179060788432584</v>
+        <v>0.09173689004176974</v>
       </c>
       <c r="C51">
-        <v>685.3829739190865</v>
+        <v>672.507767063168</v>
       </c>
       <c r="D51">
-        <v>1108.425973919086</v>
+        <v>1108.957767063168</v>
       </c>
       <c r="E51">
-        <v>77.44299999999998</v>
+        <v>90.85000000000002</v>
       </c>
       <c r="F51">
-        <v>656.943</v>
+        <v>670.35</v>
       </c>
       <c r="G51">
         <v>233.9</v>
@@ -5475,28 +5475,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M51">
-        <v>42.1100463</v>
+        <v>42.969435</v>
       </c>
       <c r="N51">
-        <v>96.12328703333333</v>
+        <v>95.26389833333332</v>
       </c>
       <c r="O51">
-        <v>20.185890277</v>
+        <v>20.00541865</v>
       </c>
       <c r="P51">
-        <v>75.93739675633333</v>
+        <v>75.25847968333332</v>
       </c>
       <c r="Q51">
-        <v>157.8373967563333</v>
+        <v>157.1584796833333</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1313284272241683</v>
+        <v>0.1328347800835395</v>
       </c>
       <c r="T51">
-        <v>1.442132154986203</v>
+        <v>1.467531428254269</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.282668756726903</v>
+        <v>3.217015381592365</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09173689004176974</v>
+        <v>0.09168317219921364</v>
       </c>
       <c r="C52">
-        <v>672.507767063168</v>
+        <v>659.6330707324473</v>
       </c>
       <c r="D52">
-        <v>1108.957767063168</v>
+        <v>1109.490070732447</v>
       </c>
       <c r="E52">
-        <v>90.85000000000002</v>
+        <v>104.2570000000001</v>
       </c>
       <c r="F52">
-        <v>670.35</v>
+        <v>683.7570000000001</v>
       </c>
       <c r="G52">
         <v>233.9</v>
@@ -5557,28 +5557,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M52">
-        <v>42.969435</v>
+        <v>43.82882370000001</v>
       </c>
       <c r="N52">
-        <v>95.26389833333332</v>
+        <v>94.4045096333333</v>
       </c>
       <c r="O52">
-        <v>20.00541865</v>
+        <v>19.82494702299999</v>
       </c>
       <c r="P52">
-        <v>75.25847968333332</v>
+        <v>74.57956261033331</v>
       </c>
       <c r="Q52">
-        <v>157.1584796833333</v>
+        <v>156.4795626103333</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1328347800835395</v>
+        <v>0.1344026167330891</v>
       </c>
       <c r="T52">
-        <v>1.467531428254269</v>
+        <v>1.493967406553685</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.217015381592365</v>
+        <v>3.153936648619965</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09168317219921364</v>
+        <v>0.09162945435665754</v>
       </c>
       <c r="C53">
-        <v>659.6330707324473</v>
+        <v>646.7588856624396</v>
       </c>
       <c r="D53">
-        <v>1109.490070732447</v>
+        <v>1110.02288566244</v>
       </c>
       <c r="E53">
-        <v>104.2570000000001</v>
+        <v>117.6640000000001</v>
       </c>
       <c r="F53">
-        <v>683.7570000000001</v>
+        <v>697.1640000000001</v>
       </c>
       <c r="G53">
         <v>233.9</v>
@@ -5639,28 +5639,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M53">
-        <v>43.82882370000001</v>
+        <v>44.68821240000001</v>
       </c>
       <c r="N53">
-        <v>94.4045096333333</v>
+        <v>93.54512093333331</v>
       </c>
       <c r="O53">
-        <v>19.82494702299999</v>
+        <v>19.64447539599999</v>
       </c>
       <c r="P53">
-        <v>74.57956261033331</v>
+        <v>73.90064553733332</v>
       </c>
       <c r="Q53">
-        <v>156.4795626103333</v>
+        <v>155.8006455373333</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1344026167330891</v>
+        <v>0.1360357799097032</v>
       </c>
       <c r="T53">
-        <v>1.493967406553685</v>
+        <v>1.521504883948909</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.153936648619965</v>
+        <v>3.093284020761888</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09162945435665754</v>
+        <v>0.09157573651410142</v>
       </c>
       <c r="C54">
-        <v>646.7588856624396</v>
+        <v>633.8852125900736</v>
       </c>
       <c r="D54">
-        <v>1110.02288566244</v>
+        <v>1110.556212590074</v>
       </c>
       <c r="E54">
-        <v>117.6640000000001</v>
+        <v>131.071</v>
       </c>
       <c r="F54">
-        <v>697.1640000000001</v>
+        <v>710.571</v>
       </c>
       <c r="G54">
         <v>233.9</v>
@@ -5721,28 +5721,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M54">
-        <v>44.68821240000001</v>
+        <v>45.5476011</v>
       </c>
       <c r="N54">
-        <v>93.54512093333331</v>
+        <v>92.68573223333331</v>
       </c>
       <c r="O54">
-        <v>19.64447539599999</v>
+        <v>19.46400376899999</v>
       </c>
       <c r="P54">
-        <v>73.90064553733332</v>
+        <v>73.22172846433332</v>
       </c>
       <c r="Q54">
-        <v>155.8006455373333</v>
+        <v>155.1217284643333</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1360357799097032</v>
+        <v>0.1377384393917052</v>
       </c>
       <c r="T54">
-        <v>1.521504883948909</v>
+        <v>1.550214168892867</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.093284020761888</v>
+        <v>3.034920171313551</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09157573651410142</v>
+        <v>0.09484949867154532</v>
       </c>
       <c r="C55">
-        <v>633.8852125900736</v>
+        <v>588.8847948042376</v>
       </c>
       <c r="D55">
-        <v>1110.556212590074</v>
+        <v>1078.962794804238</v>
       </c>
       <c r="E55">
-        <v>131.071</v>
+        <v>144.4780000000001</v>
       </c>
       <c r="F55">
-        <v>710.571</v>
+        <v>723.9780000000001</v>
       </c>
       <c r="G55">
         <v>233.9</v>
@@ -5803,45 +5803,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M55">
-        <v>45.5476011</v>
+        <v>52.05401820000001</v>
       </c>
       <c r="N55">
-        <v>92.68573223333331</v>
+        <v>86.17931513333332</v>
       </c>
       <c r="O55">
-        <v>19.46400376899999</v>
+        <v>18.097656178</v>
       </c>
       <c r="P55">
-        <v>73.22172846433332</v>
+        <v>68.08165895533332</v>
       </c>
       <c r="Q55">
-        <v>155.1217284643333</v>
+        <v>149.9816589553333</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1377384393917052</v>
+        <v>0.1395151275468376</v>
       </c>
       <c r="T55">
-        <v>1.550214168892867</v>
+        <v>1.580171683616996</v>
       </c>
       <c r="U55">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.21</v>
       </c>
       <c r="W55">
-        <v>0.050639</v>
+        <v>0.056801</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.034920171313551</v>
+        <v>2.655574691702346</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09484949867154532</v>
+        <v>0.09485740082898921</v>
       </c>
       <c r="C56">
-        <v>588.8847948042376</v>
+        <v>575.4037096367459</v>
       </c>
       <c r="D56">
-        <v>1078.962794804238</v>
+        <v>1078.888709636746</v>
       </c>
       <c r="E56">
-        <v>144.4780000000001</v>
+        <v>157.8850000000001</v>
       </c>
       <c r="F56">
-        <v>723.9780000000001</v>
+        <v>737.3850000000001</v>
       </c>
       <c r="G56">
         <v>233.9</v>
@@ -5885,28 +5885,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M56">
-        <v>52.05401820000001</v>
+        <v>53.01798150000001</v>
       </c>
       <c r="N56">
-        <v>86.17931513333332</v>
+        <v>85.2153518333333</v>
       </c>
       <c r="O56">
-        <v>18.097656178</v>
+        <v>17.89522388499999</v>
       </c>
       <c r="P56">
-        <v>68.08165895533332</v>
+        <v>67.32012794833331</v>
       </c>
       <c r="Q56">
-        <v>149.9816589553333</v>
+        <v>149.2201279483333</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1395151275468376</v>
+        <v>0.141370779619976</v>
       </c>
       <c r="T56">
-        <v>1.580171683616996</v>
+        <v>1.611460643439976</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.655574691702346</v>
+        <v>2.607291515489575</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09485740082898921</v>
+        <v>0.09486530298643311</v>
       </c>
       <c r="C57">
-        <v>575.4037096367459</v>
+        <v>561.9226346424223</v>
       </c>
       <c r="D57">
-        <v>1078.888709636746</v>
+        <v>1078.814634642422</v>
       </c>
       <c r="E57">
-        <v>157.8850000000001</v>
+        <v>171.2920000000001</v>
       </c>
       <c r="F57">
-        <v>737.3850000000001</v>
+        <v>750.7920000000001</v>
       </c>
       <c r="G57">
         <v>233.9</v>
@@ -5967,28 +5967,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M57">
-        <v>53.01798150000001</v>
+        <v>53.98194480000002</v>
       </c>
       <c r="N57">
-        <v>85.2153518333333</v>
+        <v>84.25138853333331</v>
       </c>
       <c r="O57">
-        <v>17.89522388499999</v>
+        <v>17.692791592</v>
       </c>
       <c r="P57">
-        <v>67.32012794833331</v>
+        <v>66.55859694133332</v>
       </c>
       <c r="Q57">
-        <v>149.2201279483333</v>
+        <v>148.4585969413333</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.141370779619976</v>
+        <v>0.1433107795146207</v>
       </c>
       <c r="T57">
-        <v>1.611460643439976</v>
+        <v>1.644171828709455</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.607291515489575</v>
+        <v>2.560732738427262</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09486530298643311</v>
+        <v>0.094873205143877</v>
       </c>
       <c r="C58">
-        <v>561.9226346424223</v>
+        <v>548.4415698191726</v>
       </c>
       <c r="D58">
-        <v>1078.814634642422</v>
+        <v>1078.740569819173</v>
       </c>
       <c r="E58">
-        <v>171.2920000000001</v>
+        <v>184.6990000000001</v>
       </c>
       <c r="F58">
-        <v>750.7920000000001</v>
+        <v>764.1990000000001</v>
       </c>
       <c r="G58">
         <v>233.9</v>
@@ -6049,28 +6049,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M58">
-        <v>53.98194480000002</v>
+        <v>54.94590810000001</v>
       </c>
       <c r="N58">
-        <v>84.25138853333331</v>
+        <v>83.28742523333331</v>
       </c>
       <c r="O58">
-        <v>17.692791592</v>
+        <v>17.49035929899999</v>
       </c>
       <c r="P58">
-        <v>66.55859694133332</v>
+        <v>65.79706593433332</v>
       </c>
       <c r="Q58">
-        <v>148.4585969413333</v>
+        <v>147.6970659343333</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1433107795146207</v>
+        <v>0.1453410119625047</v>
       </c>
       <c r="T58">
-        <v>1.644171828709455</v>
+        <v>1.678404464456585</v>
       </c>
       <c r="U58">
         <v>0.07190000000000001</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.560732738427262</v>
+        <v>2.51580760266538</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.094873205143877</v>
+        <v>0.0966680873013209</v>
       </c>
       <c r="C59">
-        <v>548.4415698191726</v>
+        <v>518.471061064634</v>
       </c>
       <c r="D59">
-        <v>1078.740569819173</v>
+        <v>1062.177061064634</v>
       </c>
       <c r="E59">
-        <v>184.6990000000001</v>
+        <v>198.1060000000001</v>
       </c>
       <c r="F59">
-        <v>764.1990000000001</v>
+        <v>777.6060000000001</v>
       </c>
       <c r="G59">
         <v>233.9</v>
@@ -6131,45 +6131,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M59">
-        <v>54.94590810000001</v>
+        <v>58.94253480000001</v>
       </c>
       <c r="N59">
-        <v>83.28742523333331</v>
+        <v>79.29079853333332</v>
       </c>
       <c r="O59">
-        <v>17.49035929899999</v>
+        <v>16.65106769199999</v>
       </c>
       <c r="P59">
-        <v>65.79706593433332</v>
+        <v>62.63973084133332</v>
       </c>
       <c r="Q59">
-        <v>147.6970659343333</v>
+        <v>144.5397308413333</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1453410119625047</v>
+        <v>0.1474679221460021</v>
       </c>
       <c r="T59">
-        <v>1.678404464456585</v>
+        <v>1.714267225715482</v>
       </c>
       <c r="U59">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V59">
         <v>0.21</v>
       </c>
       <c r="W59">
-        <v>0.056801</v>
+        <v>0.059882</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.51580760266538</v>
+        <v>2.345222067601567</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.0966680873013209</v>
+        <v>0.09670679945876479</v>
       </c>
       <c r="C60">
-        <v>518.4710610646341</v>
+        <v>504.7124197601987</v>
       </c>
       <c r="D60">
-        <v>1062.177061064634</v>
+        <v>1061.825419760199</v>
       </c>
       <c r="E60">
-        <v>198.106</v>
+        <v>211.513</v>
       </c>
       <c r="F60">
-        <v>777.606</v>
+        <v>791.013</v>
       </c>
       <c r="G60">
         <v>233.9</v>
@@ -6213,28 +6213,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M60">
-        <v>58.9425348</v>
+        <v>59.95878540000001</v>
       </c>
       <c r="N60">
-        <v>79.29079853333332</v>
+        <v>78.27454793333331</v>
       </c>
       <c r="O60">
-        <v>16.65106769199999</v>
+        <v>16.43765506599999</v>
       </c>
       <c r="P60">
-        <v>62.63973084133332</v>
+        <v>61.83689286733332</v>
       </c>
       <c r="Q60">
-        <v>144.5397308413333</v>
+        <v>143.7368928673333</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1474679221460021</v>
+        <v>0.1496985840457677</v>
       </c>
       <c r="T60">
-        <v>1.714267225715481</v>
+        <v>1.751879389962617</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.345222067601567</v>
+        <v>2.305472541032048</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09670679945876479</v>
+        <v>0.09674551161620867</v>
       </c>
       <c r="C61">
-        <v>504.7124197601987</v>
+        <v>490.954011205442</v>
       </c>
       <c r="D61">
-        <v>1061.825419760199</v>
+        <v>1061.474011205442</v>
       </c>
       <c r="E61">
-        <v>211.513</v>
+        <v>224.92</v>
       </c>
       <c r="F61">
-        <v>791.013</v>
+        <v>804.42</v>
       </c>
       <c r="G61">
         <v>233.9</v>
@@ -6295,28 +6295,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M61">
-        <v>59.95878540000001</v>
+        <v>60.975036</v>
       </c>
       <c r="N61">
-        <v>78.27454793333331</v>
+        <v>77.25829733333332</v>
       </c>
       <c r="O61">
-        <v>16.43765506599999</v>
+        <v>16.22424244</v>
       </c>
       <c r="P61">
-        <v>61.83689286733332</v>
+        <v>61.03405489333332</v>
       </c>
       <c r="Q61">
-        <v>143.7368928673333</v>
+        <v>142.9340548933333</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1496985840457677</v>
+        <v>0.1520407790405217</v>
       </c>
       <c r="T61">
-        <v>1.751879389962617</v>
+        <v>1.79137216242211</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.305472541032048</v>
+        <v>2.267047998681515</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09674551161620867</v>
+        <v>0.09678422377365256</v>
       </c>
       <c r="C62">
-        <v>490.954011205442</v>
+        <v>477.1958351693565</v>
       </c>
       <c r="D62">
-        <v>1061.474011205442</v>
+        <v>1061.122835169356</v>
       </c>
       <c r="E62">
-        <v>224.92</v>
+        <v>238.327</v>
       </c>
       <c r="F62">
-        <v>804.42</v>
+        <v>817.827</v>
       </c>
       <c r="G62">
         <v>233.9</v>
@@ -6377,28 +6377,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M62">
-        <v>60.975036</v>
+        <v>61.9912866</v>
       </c>
       <c r="N62">
-        <v>77.25829733333332</v>
+        <v>76.24204673333332</v>
       </c>
       <c r="O62">
-        <v>16.22424244</v>
+        <v>16.010829814</v>
       </c>
       <c r="P62">
-        <v>61.03405489333332</v>
+        <v>60.23121691933333</v>
       </c>
       <c r="Q62">
-        <v>142.9340548933333</v>
+        <v>142.1312169193333</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1520407790405217</v>
+        <v>0.1545030865991091</v>
       </c>
       <c r="T62">
-        <v>1.79137216242211</v>
+        <v>1.832890205264141</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.267047998681515</v>
+        <v>2.229883277391654</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09678422377365256</v>
+        <v>0.09682293593109645</v>
       </c>
       <c r="C63">
-        <v>477.1958351693565</v>
+        <v>463.4378914212404</v>
       </c>
       <c r="D63">
-        <v>1061.122835169356</v>
+        <v>1060.77189142124</v>
       </c>
       <c r="E63">
-        <v>238.327</v>
+        <v>251.734</v>
       </c>
       <c r="F63">
-        <v>817.827</v>
+        <v>831.234</v>
       </c>
       <c r="G63">
         <v>233.9</v>
@@ -6459,28 +6459,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M63">
-        <v>61.9912866</v>
+        <v>63.00753720000001</v>
       </c>
       <c r="N63">
-        <v>76.24204673333332</v>
+        <v>75.22579613333332</v>
       </c>
       <c r="O63">
-        <v>16.010829814</v>
+        <v>15.797417188</v>
       </c>
       <c r="P63">
-        <v>60.23121691933333</v>
+        <v>59.42837894533332</v>
       </c>
       <c r="Q63">
-        <v>142.1312169193333</v>
+        <v>141.3283789453333</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1545030865991091</v>
+        <v>0.1570949892923591</v>
       </c>
       <c r="T63">
-        <v>1.832890205264141</v>
+        <v>1.876593408255753</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.229883277391654</v>
+        <v>2.193917418078885</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09682293593109645</v>
+        <v>0.09686164808854034</v>
       </c>
       <c r="C64">
-        <v>463.4378914212404</v>
+        <v>449.6801797306971</v>
       </c>
       <c r="D64">
-        <v>1060.77189142124</v>
+        <v>1060.421179730697</v>
       </c>
       <c r="E64">
-        <v>251.734</v>
+        <v>265.1410000000001</v>
       </c>
       <c r="F64">
-        <v>831.234</v>
+        <v>844.6410000000001</v>
       </c>
       <c r="G64">
         <v>233.9</v>
@@ -6541,28 +6541,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M64">
-        <v>63.00753720000001</v>
+        <v>64.02378780000001</v>
       </c>
       <c r="N64">
-        <v>75.22579613333332</v>
+        <v>74.20954553333331</v>
       </c>
       <c r="O64">
-        <v>15.797417188</v>
+        <v>15.584004562</v>
       </c>
       <c r="P64">
-        <v>59.42837894533332</v>
+        <v>58.62554097133332</v>
       </c>
       <c r="Q64">
-        <v>141.3283789453333</v>
+        <v>140.5255409713333</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1570949892923591</v>
+        <v>0.1598269948338928</v>
       </c>
       <c r="T64">
-        <v>1.876593408255753</v>
+        <v>1.922658946544208</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.193917418078885</v>
+        <v>2.159093332077633</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09686164808854034</v>
+        <v>0.09690036024598424</v>
       </c>
       <c r="C65">
-        <v>449.6801797306971</v>
+        <v>435.9226998676345</v>
       </c>
       <c r="D65">
-        <v>1060.421179730697</v>
+        <v>1060.070699867634</v>
       </c>
       <c r="E65">
-        <v>265.1410000000001</v>
+        <v>278.548</v>
       </c>
       <c r="F65">
-        <v>844.6410000000001</v>
+        <v>858.048</v>
       </c>
       <c r="G65">
         <v>233.9</v>
@@ -6623,28 +6623,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M65">
-        <v>64.02378780000001</v>
+        <v>65.0400384</v>
       </c>
       <c r="N65">
-        <v>74.20954553333331</v>
+        <v>73.19329493333332</v>
       </c>
       <c r="O65">
-        <v>15.584004562</v>
+        <v>15.370591936</v>
       </c>
       <c r="P65">
-        <v>58.62554097133332</v>
+        <v>57.82270299733332</v>
       </c>
       <c r="Q65">
-        <v>140.5255409713333</v>
+        <v>139.7227029973333</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1598269948338928</v>
+        <v>0.1627107784610673</v>
       </c>
       <c r="T65">
-        <v>1.922658946544208</v>
+        <v>1.971283681404244</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.159093332077633</v>
+        <v>2.12535749876392</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09690036024598424</v>
+        <v>0.09693907240342814</v>
       </c>
       <c r="C66">
-        <v>435.9226998676345</v>
+        <v>422.1654516022642</v>
       </c>
       <c r="D66">
-        <v>1060.070699867634</v>
+        <v>1059.720451602264</v>
       </c>
       <c r="E66">
-        <v>278.548</v>
+        <v>291.955</v>
       </c>
       <c r="F66">
-        <v>858.048</v>
+        <v>871.455</v>
       </c>
       <c r="G66">
         <v>233.9</v>
@@ -6705,28 +6705,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M66">
-        <v>65.0400384</v>
+        <v>66.05628900000001</v>
       </c>
       <c r="N66">
-        <v>73.19329493333332</v>
+        <v>72.17704433333331</v>
       </c>
       <c r="O66">
-        <v>15.370591936</v>
+        <v>15.15717930999999</v>
       </c>
       <c r="P66">
-        <v>57.82270299733332</v>
+        <v>57.01986502333332</v>
       </c>
       <c r="Q66">
-        <v>139.7227029973333</v>
+        <v>138.9198650233333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1627107784610673</v>
+        <v>0.1657593497240804</v>
       </c>
       <c r="T66">
-        <v>1.971283681404244</v>
+        <v>2.022686972541997</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.12535749876392</v>
+        <v>2.092659691090629</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09693907240342814</v>
+        <v>0.09697778456087203</v>
       </c>
       <c r="C67">
-        <v>422.1654516022642</v>
+        <v>408.4084347051025</v>
       </c>
       <c r="D67">
-        <v>1059.720451602264</v>
+        <v>1059.370434705103</v>
       </c>
       <c r="E67">
-        <v>291.955</v>
+        <v>305.3620000000001</v>
       </c>
       <c r="F67">
-        <v>871.455</v>
+        <v>884.8620000000001</v>
       </c>
       <c r="G67">
         <v>233.9</v>
@@ -6787,28 +6787,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M67">
-        <v>66.05628900000001</v>
+        <v>67.07253960000001</v>
       </c>
       <c r="N67">
-        <v>72.17704433333331</v>
+        <v>71.16079373333331</v>
       </c>
       <c r="O67">
-        <v>15.15717930999999</v>
+        <v>14.94376668399999</v>
       </c>
       <c r="P67">
-        <v>57.01986502333332</v>
+        <v>56.21702704933331</v>
       </c>
       <c r="Q67">
-        <v>138.9198650233333</v>
+        <v>138.1170270493333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1657593497240804</v>
+        <v>0.1689872487084471</v>
       </c>
       <c r="T67">
-        <v>2.022686972541997</v>
+        <v>2.077113986687853</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.092659691090629</v>
+        <v>2.060952726074104</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09697778456087203</v>
+        <v>0.09701649671831591</v>
       </c>
       <c r="C68">
-        <v>408.4084347051025</v>
+        <v>394.6516489469678</v>
       </c>
       <c r="D68">
-        <v>1059.370434705103</v>
+        <v>1059.020648946968</v>
       </c>
       <c r="E68">
-        <v>305.3620000000001</v>
+        <v>318.7690000000001</v>
       </c>
       <c r="F68">
-        <v>884.8620000000001</v>
+        <v>898.2690000000001</v>
       </c>
       <c r="G68">
         <v>233.9</v>
@@ -6869,28 +6869,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M68">
-        <v>67.07253960000001</v>
+        <v>68.08879020000002</v>
       </c>
       <c r="N68">
-        <v>71.16079373333331</v>
+        <v>70.1445431333333</v>
       </c>
       <c r="O68">
-        <v>14.94376668399999</v>
+        <v>14.73035405799999</v>
       </c>
       <c r="P68">
-        <v>56.21702704933331</v>
+        <v>55.41418907533331</v>
       </c>
       <c r="Q68">
-        <v>138.1170270493333</v>
+        <v>137.3141890753333</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1689872487084471</v>
+        <v>0.1724107779342907</v>
       </c>
       <c r="T68">
-        <v>2.077113986687853</v>
+        <v>2.134839607751639</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.060952726074104</v>
+        <v>2.030192237625236</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09701649671831591</v>
+        <v>0.0970552088757598</v>
       </c>
       <c r="C69">
-        <v>394.6516489469678</v>
+        <v>380.8950940989813</v>
       </c>
       <c r="D69">
-        <v>1059.020648946968</v>
+        <v>1058.671094098981</v>
       </c>
       <c r="E69">
-        <v>318.7690000000001</v>
+        <v>332.176</v>
       </c>
       <c r="F69">
-        <v>898.2690000000001</v>
+        <v>911.676</v>
       </c>
       <c r="G69">
         <v>233.9</v>
@@ -6951,28 +6951,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M69">
-        <v>68.08879020000002</v>
+        <v>69.10504080000001</v>
       </c>
       <c r="N69">
-        <v>70.1445431333333</v>
+        <v>69.12829253333331</v>
       </c>
       <c r="O69">
-        <v>14.73035405799999</v>
+        <v>14.51694143199999</v>
       </c>
       <c r="P69">
-        <v>55.41418907533331</v>
+        <v>54.61135110133331</v>
       </c>
       <c r="Q69">
-        <v>137.3141890753333</v>
+        <v>136.5113511013333</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1724107779342907</v>
+        <v>0.1760482777367494</v>
       </c>
       <c r="T69">
-        <v>2.134839607751639</v>
+        <v>2.196173080131912</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.030192237625236</v>
+        <v>2.000336469424866</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0970552088757598</v>
+        <v>0.1048343410332037</v>
       </c>
       <c r="C70">
-        <v>380.8950940989813</v>
+        <v>301.6366874358016</v>
       </c>
       <c r="D70">
-        <v>1058.671094098981</v>
+        <v>992.8196874358017</v>
       </c>
       <c r="E70">
-        <v>332.176</v>
+        <v>345.5830000000001</v>
       </c>
       <c r="F70">
-        <v>911.676</v>
+        <v>925.0830000000001</v>
       </c>
       <c r="G70">
         <v>233.9</v>
@@ -7033,45 +7033,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M70">
-        <v>69.10504080000001</v>
+        <v>83.25747</v>
       </c>
       <c r="N70">
-        <v>69.12829253333331</v>
+        <v>54.97586333333332</v>
       </c>
       <c r="O70">
-        <v>14.51694143199999</v>
+        <v>11.5449313</v>
       </c>
       <c r="P70">
-        <v>54.61135110133331</v>
+        <v>43.43093203333333</v>
       </c>
       <c r="Q70">
-        <v>136.5113511013333</v>
+        <v>125.3309320333333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1760482777367494</v>
+        <v>0.1799204549458184</v>
       </c>
       <c r="T70">
-        <v>2.196173080131912</v>
+        <v>2.261463550730267</v>
       </c>
       <c r="U70">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V70">
         <v>0.21</v>
       </c>
       <c r="W70">
-        <v>0.059882</v>
+        <v>0.0711</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y70">
-        <v>2.000336469424866</v>
+        <v>1.660311481159989</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1048343410332037</v>
+        <v>0.1049852331906476</v>
       </c>
       <c r="C71">
-        <v>301.6366874358016</v>
+        <v>287.0332603815008</v>
       </c>
       <c r="D71">
-        <v>992.8196874358017</v>
+        <v>991.6232603815008</v>
       </c>
       <c r="E71">
-        <v>345.5830000000001</v>
+        <v>358.9900000000001</v>
       </c>
       <c r="F71">
-        <v>925.0830000000001</v>
+        <v>938.4900000000001</v>
       </c>
       <c r="G71">
         <v>233.9</v>
@@ -7115,28 +7115,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M71">
-        <v>83.25747</v>
+        <v>84.4641</v>
       </c>
       <c r="N71">
-        <v>54.97586333333332</v>
+        <v>53.76923333333332</v>
       </c>
       <c r="O71">
-        <v>11.5449313</v>
+        <v>11.291539</v>
       </c>
       <c r="P71">
-        <v>43.43093203333333</v>
+        <v>42.47769433333332</v>
       </c>
       <c r="Q71">
-        <v>125.3309320333333</v>
+        <v>124.3776943333333</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1799204549458184</v>
+        <v>0.1840507773021587</v>
       </c>
       <c r="T71">
-        <v>2.261463550730267</v>
+        <v>2.331106719368513</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.660311481159989</v>
+        <v>1.636592745714846</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1049852331906476</v>
+        <v>0.1051361253480915</v>
       </c>
       <c r="C72">
-        <v>287.0332603815008</v>
+        <v>272.4327134368386</v>
       </c>
       <c r="D72">
-        <v>991.6232603815008</v>
+        <v>990.4297134368388</v>
       </c>
       <c r="E72">
-        <v>358.9900000000001</v>
+        <v>372.3970000000002</v>
       </c>
       <c r="F72">
-        <v>938.4900000000001</v>
+        <v>951.8970000000002</v>
       </c>
       <c r="G72">
         <v>233.9</v>
@@ -7197,28 +7197,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M72">
-        <v>84.4641</v>
+        <v>85.67073000000001</v>
       </c>
       <c r="N72">
-        <v>53.76923333333332</v>
+        <v>52.56260333333331</v>
       </c>
       <c r="O72">
-        <v>11.291539</v>
+        <v>11.0381467</v>
       </c>
       <c r="P72">
-        <v>42.47769433333332</v>
+        <v>41.52445663333332</v>
       </c>
       <c r="Q72">
-        <v>124.3776943333333</v>
+        <v>123.4244566333333</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1840507773021587</v>
+        <v>0.1884659494761776</v>
       </c>
       <c r="T72">
-        <v>2.331106719368513</v>
+        <v>2.405552865154224</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.636592745714846</v>
+        <v>1.613542143662524</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1051361253480915</v>
+        <v>0.1052870175055354</v>
       </c>
       <c r="C73">
-        <v>272.4327134368391</v>
+        <v>257.8350362145642</v>
       </c>
       <c r="D73">
-        <v>990.4297134368389</v>
+        <v>989.2390362145641</v>
       </c>
       <c r="E73">
-        <v>372.3969999999999</v>
+        <v>385.804</v>
       </c>
       <c r="F73">
-        <v>951.8969999999999</v>
+        <v>965.304</v>
       </c>
       <c r="G73">
         <v>233.9</v>
@@ -7279,28 +7279,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M73">
-        <v>85.67072999999999</v>
+        <v>86.87736</v>
       </c>
       <c r="N73">
-        <v>52.56260333333333</v>
+        <v>51.35597333333332</v>
       </c>
       <c r="O73">
-        <v>11.0381467</v>
+        <v>10.7847544</v>
       </c>
       <c r="P73">
-        <v>41.52445663333333</v>
+        <v>40.57121893333333</v>
       </c>
       <c r="Q73">
-        <v>123.4244566333333</v>
+        <v>122.4712189333333</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1884659494761775</v>
+        <v>0.1931964910911977</v>
       </c>
       <c r="T73">
-        <v>2.405552865154223</v>
+        <v>2.48531659278177</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.613542143662524</v>
+        <v>1.591131836111656</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1052870175055354</v>
+        <v>0.1054379096629793</v>
       </c>
       <c r="C74">
-        <v>257.8350362145642</v>
+        <v>243.2402183773138</v>
       </c>
       <c r="D74">
-        <v>989.2390362145641</v>
+        <v>988.0512183773138</v>
       </c>
       <c r="E74">
-        <v>385.804</v>
+        <v>399.211</v>
       </c>
       <c r="F74">
-        <v>965.304</v>
+        <v>978.711</v>
       </c>
       <c r="G74">
         <v>233.9</v>
@@ -7361,28 +7361,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M74">
-        <v>86.87736</v>
+        <v>88.08399</v>
       </c>
       <c r="N74">
-        <v>51.35597333333332</v>
+        <v>50.14934333333332</v>
       </c>
       <c r="O74">
-        <v>10.7847544</v>
+        <v>10.5313621</v>
       </c>
       <c r="P74">
-        <v>40.57121893333333</v>
+        <v>39.61798123333332</v>
       </c>
       <c r="Q74">
-        <v>122.4712189333333</v>
+        <v>121.5179812333333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1931964910911977</v>
+        <v>0.1982774431962195</v>
       </c>
       <c r="T74">
-        <v>2.48531659278177</v>
+        <v>2.570988744678024</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.591131836111656</v>
+        <v>1.569335509589578</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1054379096629793</v>
+        <v>0.1055888018204232</v>
       </c>
       <c r="C75">
-        <v>243.2402183773138</v>
+        <v>228.6482496373166</v>
       </c>
       <c r="D75">
-        <v>988.0512183773138</v>
+        <v>986.8662496373166</v>
       </c>
       <c r="E75">
-        <v>399.211</v>
+        <v>412.6180000000001</v>
       </c>
       <c r="F75">
-        <v>978.711</v>
+        <v>992.1180000000001</v>
       </c>
       <c r="G75">
         <v>233.9</v>
@@ -7443,28 +7443,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M75">
-        <v>88.08399</v>
+        <v>89.29062</v>
       </c>
       <c r="N75">
-        <v>50.14934333333332</v>
+        <v>48.94271333333332</v>
       </c>
       <c r="O75">
-        <v>10.5313621</v>
+        <v>10.2779698</v>
       </c>
       <c r="P75">
-        <v>39.61798123333332</v>
+        <v>38.66474353333332</v>
       </c>
       <c r="Q75">
-        <v>121.5179812333333</v>
+        <v>120.5647435333333</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1982774431962195</v>
+        <v>0.2037492377708583</v>
       </c>
       <c r="T75">
-        <v>2.570988744678024</v>
+        <v>2.66325106210476</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.569335509589578</v>
+        <v>1.548128272973503</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1055888018204232</v>
+        <v>0.105739693977867</v>
       </c>
       <c r="C76">
-        <v>228.6482496373166</v>
+        <v>214.0591197560934</v>
       </c>
       <c r="D76">
-        <v>986.8662496373166</v>
+        <v>985.6841197560934</v>
       </c>
       <c r="E76">
-        <v>412.6180000000001</v>
+        <v>426.0250000000001</v>
       </c>
       <c r="F76">
-        <v>992.1180000000001</v>
+        <v>1005.525</v>
       </c>
       <c r="G76">
         <v>233.9</v>
@@ -7525,28 +7525,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M76">
-        <v>89.29062</v>
+        <v>90.49725000000001</v>
       </c>
       <c r="N76">
-        <v>48.94271333333332</v>
+        <v>47.73608333333331</v>
       </c>
       <c r="O76">
-        <v>10.2779698</v>
+        <v>10.0245775</v>
       </c>
       <c r="P76">
-        <v>38.66474353333332</v>
+        <v>37.71150583333332</v>
       </c>
       <c r="Q76">
-        <v>120.5647435333333</v>
+        <v>119.6115058333333</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2037492377708583</v>
+        <v>0.2096587759114682</v>
       </c>
       <c r="T76">
-        <v>2.66325106210476</v>
+        <v>2.762894364925634</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.548128272973503</v>
+        <v>1.527486562667189</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.105739693977867</v>
+        <v>0.1058905861353109</v>
       </c>
       <c r="C77">
-        <v>214.0591197560934</v>
+        <v>199.4728185441643</v>
       </c>
       <c r="D77">
-        <v>985.6841197560934</v>
+        <v>984.5048185441643</v>
       </c>
       <c r="E77">
-        <v>426.0250000000001</v>
+        <v>439.432</v>
       </c>
       <c r="F77">
-        <v>1005.525</v>
+        <v>1018.932</v>
       </c>
       <c r="G77">
         <v>233.9</v>
@@ -7607,28 +7607,28 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M77">
-        <v>90.49725000000001</v>
+        <v>91.70388</v>
       </c>
       <c r="N77">
-        <v>47.73608333333331</v>
+        <v>46.52945333333332</v>
       </c>
       <c r="O77">
-        <v>10.0245775</v>
+        <v>9.771185199999998</v>
       </c>
       <c r="P77">
-        <v>37.71150583333332</v>
+        <v>36.75826813333332</v>
       </c>
       <c r="Q77">
-        <v>119.6115058333333</v>
+        <v>118.6582681333333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2096587759114682</v>
+        <v>0.2160607755637956</v>
       </c>
       <c r="T77">
-        <v>2.762894364925634</v>
+        <v>2.870841276314915</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.527486562667189</v>
+        <v>1.507388055263674</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1058905861353109</v>
+        <v>0.1433690905744905</v>
       </c>
       <c r="C78">
-        <v>199.4728185441643</v>
+        <v>-39.47443689158263</v>
       </c>
       <c r="D78">
-        <v>984.5048185441643</v>
+        <v>758.9645631084176</v>
       </c>
       <c r="E78">
-        <v>439.432</v>
+        <v>452.8390000000002</v>
       </c>
       <c r="F78">
-        <v>1018.932</v>
+        <v>1032.339</v>
       </c>
       <c r="G78">
         <v>233.9</v>
@@ -7689,45 +7689,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M78">
-        <v>91.70388</v>
+        <v>151.5473652</v>
       </c>
       <c r="N78">
-        <v>46.52945333333332</v>
+        <v>-13.31403186666671</v>
       </c>
       <c r="O78">
-        <v>9.771185199999998</v>
+        <v>-2.795946692000009</v>
       </c>
       <c r="P78">
-        <v>36.75826813333332</v>
+        <v>-10.5180851746667</v>
       </c>
       <c r="Q78">
-        <v>118.6582681333333</v>
+        <v>71.3819148253333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2160607755637956</v>
+        <v>0.2260226634795562</v>
       </c>
       <c r="T78">
-        <v>2.870841276314915</v>
+        <v>3.038813018038084</v>
       </c>
       <c r="U78">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.21</v>
+        <v>0.1915506743498302</v>
       </c>
       <c r="W78">
-        <v>0.0711</v>
+        <v>0.1186803610054449</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y78">
-        <v>1.507388055263674</v>
+        <v>0.9121460683325249</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1433690905744905</v>
+        <v>0.1443790905744906</v>
       </c>
       <c r="C79">
-        <v>-39.47443689158263</v>
+        <v>-57.53830439799833</v>
       </c>
       <c r="D79">
-        <v>758.9645631084176</v>
+        <v>754.3076956020018</v>
       </c>
       <c r="E79">
-        <v>452.8390000000002</v>
+        <v>466.2460000000001</v>
       </c>
       <c r="F79">
-        <v>1032.339</v>
+        <v>1045.746</v>
       </c>
       <c r="G79">
         <v>233.9</v>
@@ -7771,37 +7771,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M79">
-        <v>151.5473652</v>
+        <v>153.5155128</v>
       </c>
       <c r="N79">
-        <v>-13.31403186666671</v>
+        <v>-15.28217946666672</v>
       </c>
       <c r="O79">
-        <v>-2.795946692000009</v>
+        <v>-3.209257688000011</v>
       </c>
       <c r="P79">
-        <v>-10.5180851746667</v>
+        <v>-12.07292177866671</v>
       </c>
       <c r="Q79">
-        <v>71.3819148253333</v>
+        <v>69.8270782213333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2260226634795562</v>
+        <v>0.234214602728627</v>
       </c>
       <c r="T79">
-        <v>3.038813018038084</v>
+        <v>3.176940882494361</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1915506743498302</v>
+        <v>0.1890948964735503</v>
       </c>
       <c r="W79">
-        <v>0.1186803610054449</v>
+        <v>0.1190408691976828</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9121460683325249</v>
+        <v>0.9004518879692873</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1443790905744906</v>
+        <v>0.1453890905744905</v>
       </c>
       <c r="C80">
-        <v>-57.53830439799833</v>
+        <v>-75.54537304020482</v>
       </c>
       <c r="D80">
-        <v>754.3076956020018</v>
+        <v>749.7076269597952</v>
       </c>
       <c r="E80">
-        <v>466.2460000000001</v>
+        <v>479.653</v>
       </c>
       <c r="F80">
-        <v>1045.746</v>
+        <v>1059.153</v>
       </c>
       <c r="G80">
         <v>233.9</v>
@@ -7853,37 +7853,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M80">
-        <v>153.5155128</v>
+        <v>155.4836604</v>
       </c>
       <c r="N80">
-        <v>-15.28217946666672</v>
+        <v>-17.2503270666667</v>
       </c>
       <c r="O80">
-        <v>-3.209257688000011</v>
+        <v>-3.622568684000007</v>
       </c>
       <c r="P80">
-        <v>-12.07292177866671</v>
+        <v>-13.62775838266669</v>
       </c>
       <c r="Q80">
-        <v>69.8270782213333</v>
+        <v>68.27224161733331</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.234214602728627</v>
+        <v>0.2431867266680854</v>
       </c>
       <c r="T80">
-        <v>3.176940882494361</v>
+        <v>3.328223781660759</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1890948964735503</v>
+        <v>0.186701290189075</v>
       </c>
       <c r="W80">
-        <v>0.1190408691976828</v>
+        <v>0.1193922506002438</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.9004518879692873</v>
+        <v>0.8890537628051192</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1453890905744905</v>
+        <v>0.1463990905744905</v>
       </c>
       <c r="C81">
-        <v>-75.54537304020482</v>
+        <v>-93.49667566574919</v>
       </c>
       <c r="D81">
-        <v>749.7076269597952</v>
+        <v>745.163324334251</v>
       </c>
       <c r="E81">
-        <v>479.653</v>
+        <v>493.0600000000002</v>
       </c>
       <c r="F81">
-        <v>1059.153</v>
+        <v>1072.56</v>
       </c>
       <c r="G81">
         <v>233.9</v>
@@ -7935,37 +7935,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M81">
-        <v>155.4836604</v>
+        <v>157.451808</v>
       </c>
       <c r="N81">
-        <v>-17.2503270666667</v>
+        <v>-19.21847466666671</v>
       </c>
       <c r="O81">
-        <v>-3.622568684000007</v>
+        <v>-4.035879680000009</v>
       </c>
       <c r="P81">
-        <v>-13.62775838266669</v>
+        <v>-15.1825949866667</v>
       </c>
       <c r="Q81">
-        <v>68.27224161733331</v>
+        <v>66.71740501333331</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2431867266680854</v>
+        <v>0.2530560630014897</v>
       </c>
       <c r="T81">
-        <v>3.328223781660759</v>
+        <v>3.494634970743798</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.186701290189075</v>
+        <v>0.1843675240617116</v>
       </c>
       <c r="W81">
-        <v>0.1193922506002438</v>
+        <v>0.1197348474677408</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8890537628051192</v>
+        <v>0.8779405907700552</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1463990905744905</v>
+        <v>0.1474090905744905</v>
       </c>
       <c r="C82">
-        <v>-93.49667566574919</v>
+        <v>-111.3932202309094</v>
       </c>
       <c r="D82">
-        <v>745.163324334251</v>
+        <v>740.6737797690907</v>
       </c>
       <c r="E82">
-        <v>493.0600000000002</v>
+        <v>506.4670000000001</v>
       </c>
       <c r="F82">
-        <v>1072.56</v>
+        <v>1085.967</v>
       </c>
       <c r="G82">
         <v>233.9</v>
@@ -8017,37 +8017,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M82">
-        <v>157.451808</v>
+        <v>159.4199556</v>
       </c>
       <c r="N82">
-        <v>-19.21847466666671</v>
+        <v>-21.18662226666672</v>
       </c>
       <c r="O82">
-        <v>-4.035879680000009</v>
+        <v>-4.44919067600001</v>
       </c>
       <c r="P82">
-        <v>-15.1825949866667</v>
+        <v>-16.73743159066671</v>
       </c>
       <c r="Q82">
-        <v>66.71740501333331</v>
+        <v>65.1625684093333</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2530560630014897</v>
+        <v>0.2639642768436734</v>
       </c>
       <c r="T82">
-        <v>3.494634970743798</v>
+        <v>3.678563127098735</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1843675240617116</v>
+        <v>0.1820913817893448</v>
       </c>
       <c r="W82">
-        <v>0.1197348474677408</v>
+        <v>0.1200689851533242</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8779405907700552</v>
+        <v>0.8671018180444989</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1474090905744905</v>
+        <v>0.1484190905744905</v>
       </c>
       <c r="C83">
-        <v>-111.3932202309094</v>
+        <v>-129.2359905460432</v>
       </c>
       <c r="D83">
-        <v>740.6737797690907</v>
+        <v>736.2380094539568</v>
       </c>
       <c r="E83">
-        <v>506.4670000000001</v>
+        <v>519.874</v>
       </c>
       <c r="F83">
-        <v>1085.967</v>
+        <v>1099.374</v>
       </c>
       <c r="G83">
         <v>233.9</v>
@@ -8099,37 +8099,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M83">
-        <v>159.4199556</v>
+        <v>161.3881032</v>
       </c>
       <c r="N83">
-        <v>-21.18662226666672</v>
+        <v>-23.1547698666667</v>
       </c>
       <c r="O83">
-        <v>-4.44919067600001</v>
+        <v>-4.862501672000007</v>
       </c>
       <c r="P83">
-        <v>-16.73743159066671</v>
+        <v>-18.29226819466669</v>
       </c>
       <c r="Q83">
-        <v>65.1625684093333</v>
+        <v>63.60773180533332</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2639642768436734</v>
+        <v>0.2760845144460997</v>
       </c>
       <c r="T83">
-        <v>3.678563127098735</v>
+        <v>3.882927745270886</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1820913817893448</v>
+        <v>0.1798707551821576</v>
       </c>
       <c r="W83">
-        <v>0.1200689851533242</v>
+        <v>0.1203949731392593</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8671018180444989</v>
+        <v>0.8565274056293222</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1484190905744905</v>
+        <v>0.1494290905744906</v>
       </c>
       <c r="C84">
-        <v>-129.2359905460432</v>
+        <v>-147.0259469943132</v>
       </c>
       <c r="D84">
-        <v>736.2380094539568</v>
+        <v>731.855053005687</v>
       </c>
       <c r="E84">
-        <v>519.874</v>
+        <v>533.2810000000002</v>
       </c>
       <c r="F84">
-        <v>1099.374</v>
+        <v>1112.781</v>
       </c>
       <c r="G84">
         <v>233.9</v>
@@ -8181,37 +8181,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M84">
-        <v>161.3881032</v>
+        <v>163.3562508000001</v>
       </c>
       <c r="N84">
-        <v>-23.1547698666667</v>
+        <v>-25.12291746666673</v>
       </c>
       <c r="O84">
-        <v>-4.862501672000007</v>
+        <v>-5.275812668000014</v>
       </c>
       <c r="P84">
-        <v>-18.29226819466669</v>
+        <v>-19.84710479866672</v>
       </c>
       <c r="Q84">
-        <v>63.60773180533332</v>
+        <v>62.05289520133329</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2760845144460997</v>
+        <v>0.2896306623546938</v>
       </c>
       <c r="T84">
-        <v>3.882927745270886</v>
+        <v>4.111335259698587</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1798707551821576</v>
+        <v>0.1777036376498425</v>
       </c>
       <c r="W84">
-        <v>0.1203949731392593</v>
+        <v>0.1207131059930031</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8565274056293222</v>
+        <v>0.8462077983325831</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1494290905744906</v>
+        <v>0.1504390905744905</v>
       </c>
       <c r="C85">
-        <v>-147.0259469943132</v>
+        <v>-164.7640272248905</v>
       </c>
       <c r="D85">
-        <v>731.855053005687</v>
+        <v>727.5239727751097</v>
       </c>
       <c r="E85">
-        <v>533.2810000000002</v>
+        <v>546.6880000000001</v>
       </c>
       <c r="F85">
-        <v>1112.781</v>
+        <v>1126.188</v>
       </c>
       <c r="G85">
         <v>233.9</v>
@@ -8263,37 +8263,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M85">
-        <v>163.3562508000001</v>
+        <v>165.3243984</v>
       </c>
       <c r="N85">
-        <v>-25.12291746666673</v>
+        <v>-27.09106506666672</v>
       </c>
       <c r="O85">
-        <v>-5.275812668000014</v>
+        <v>-5.68912366400001</v>
       </c>
       <c r="P85">
-        <v>-19.84710479866672</v>
+        <v>-21.4019414026667</v>
       </c>
       <c r="Q85">
-        <v>62.05289520133329</v>
+        <v>60.4980585973333</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2896306623546938</v>
+        <v>0.3048700787518622</v>
       </c>
       <c r="T85">
-        <v>4.111335259698587</v>
+        <v>4.368293713429749</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1777036376498425</v>
+        <v>0.175588118154011</v>
       </c>
       <c r="W85">
-        <v>0.1207131059930031</v>
+        <v>0.1210236642549912</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8462077983325831</v>
+        <v>0.836133895971481</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1504390905744905</v>
+        <v>0.1514490905744905</v>
       </c>
       <c r="C86">
-        <v>-164.7640272248905</v>
+        <v>-182.4511468216907</v>
       </c>
       <c r="D86">
-        <v>727.5239727751097</v>
+        <v>723.2438531783093</v>
       </c>
       <c r="E86">
-        <v>546.6880000000001</v>
+        <v>560.095</v>
       </c>
       <c r="F86">
-        <v>1126.188</v>
+        <v>1139.595</v>
       </c>
       <c r="G86">
         <v>233.9</v>
@@ -8345,37 +8345,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M86">
-        <v>165.3243984</v>
+        <v>167.292546</v>
       </c>
       <c r="N86">
-        <v>-27.09106506666672</v>
+        <v>-29.0592126666667</v>
       </c>
       <c r="O86">
-        <v>-5.68912366400001</v>
+        <v>-6.102434660000005</v>
       </c>
       <c r="P86">
-        <v>-21.4019414026667</v>
+        <v>-22.95677800666669</v>
       </c>
       <c r="Q86">
-        <v>60.4980585973333</v>
+        <v>58.94322199333332</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3048700787518621</v>
+        <v>0.3221414173353195</v>
       </c>
       <c r="T86">
-        <v>4.368293713429746</v>
+        <v>4.659513294325062</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.175588118154011</v>
+        <v>0.1735223755874933</v>
       </c>
       <c r="W86">
-        <v>0.1210236642549912</v>
+        <v>0.121326915263756</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.836133895971481</v>
+        <v>0.8262970266071108</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1514490905744905</v>
+        <v>0.1524590905744905</v>
       </c>
       <c r="C87">
-        <v>-182.4511468216907</v>
+        <v>-200.0881999486427</v>
       </c>
       <c r="D87">
-        <v>723.2438531783093</v>
+        <v>719.0138000513573</v>
       </c>
       <c r="E87">
-        <v>560.095</v>
+        <v>573.502</v>
       </c>
       <c r="F87">
-        <v>1139.595</v>
+        <v>1153.002</v>
       </c>
       <c r="G87">
         <v>233.9</v>
@@ -8427,37 +8427,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M87">
-        <v>167.292546</v>
+        <v>169.2606936</v>
       </c>
       <c r="N87">
-        <v>-29.0592126666667</v>
+        <v>-31.02736026666668</v>
       </c>
       <c r="O87">
-        <v>-6.102434660000005</v>
+        <v>-6.515745656000002</v>
       </c>
       <c r="P87">
-        <v>-22.95677800666669</v>
+        <v>-24.51161461066668</v>
       </c>
       <c r="Q87">
-        <v>58.94322199333332</v>
+        <v>57.38838538933333</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3221414173353195</v>
+        <v>0.341880090002128</v>
       </c>
       <c r="T87">
-        <v>4.659513294325062</v>
+        <v>4.992335672491138</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1735223755874933</v>
+        <v>0.1715046735457783</v>
       </c>
       <c r="W87">
-        <v>0.121326915263756</v>
+        <v>0.1216231139234798</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8262970266071108</v>
+        <v>0.8166889216465631</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1524590905744905</v>
+        <v>0.1534690905744905</v>
       </c>
       <c r="C88">
-        <v>-200.0881999486427</v>
+        <v>-217.6760599724421</v>
       </c>
       <c r="D88">
-        <v>719.0138000513573</v>
+        <v>714.832940027558</v>
       </c>
       <c r="E88">
-        <v>573.502</v>
+        <v>586.9090000000001</v>
       </c>
       <c r="F88">
-        <v>1153.002</v>
+        <v>1166.409</v>
       </c>
       <c r="G88">
         <v>233.9</v>
@@ -8509,37 +8509,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M88">
-        <v>169.2606936</v>
+        <v>171.2288412</v>
       </c>
       <c r="N88">
-        <v>-31.02736026666668</v>
+        <v>-32.99550786666671</v>
       </c>
       <c r="O88">
-        <v>-6.515745656000002</v>
+        <v>-6.92905665200001</v>
       </c>
       <c r="P88">
-        <v>-24.51161461066668</v>
+        <v>-26.0664512146667</v>
       </c>
       <c r="Q88">
-        <v>57.38838538933333</v>
+        <v>55.83354878533331</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.341880090002128</v>
+        <v>0.3646554815407532</v>
       </c>
       <c r="T88">
-        <v>4.992335672491138</v>
+        <v>5.376361493451994</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.1715046735457783</v>
+        <v>0.1695333554590451</v>
       </c>
       <c r="W88">
-        <v>0.1216231139234798</v>
+        <v>0.1219125034186122</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8166889216465631</v>
+        <v>0.8073016926621197</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1534690905744905</v>
+        <v>0.2039276999208101</v>
       </c>
       <c r="C89">
-        <v>-217.6760599724421</v>
+        <v>-391.9955352346036</v>
       </c>
       <c r="D89">
-        <v>714.832940027558</v>
+        <v>553.9204647653964</v>
       </c>
       <c r="E89">
-        <v>586.9090000000001</v>
+        <v>600.316</v>
       </c>
       <c r="F89">
-        <v>1166.409</v>
+        <v>1179.816</v>
       </c>
       <c r="G89">
         <v>233.9</v>
@@ -8591,45 +8591,45 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M89">
-        <v>171.2288412</v>
+        <v>236.9070528</v>
       </c>
       <c r="N89">
-        <v>-32.99550786666671</v>
+        <v>-98.67371946666668</v>
       </c>
       <c r="O89">
-        <v>-6.92905665200001</v>
+        <v>-20.721481088</v>
       </c>
       <c r="P89">
-        <v>-26.0664512146667</v>
+        <v>-77.95223837866668</v>
       </c>
       <c r="Q89">
-        <v>55.83354878533331</v>
+        <v>3.947761621333328</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3646554815407532</v>
+        <v>0.4072985162218125</v>
       </c>
       <c r="T89">
-        <v>5.376361493451994</v>
+        <v>6.095384320079745</v>
       </c>
       <c r="U89">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1695333554590451</v>
+        <v>0.122533287451373</v>
       </c>
       <c r="W89">
-        <v>0.1219125034186122</v>
+        <v>0.1761953158797643</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y89">
-        <v>0.8073016926621197</v>
+        <v>0.5834918450065381</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2039276999208101</v>
+        <v>0.2054776999208101</v>
       </c>
       <c r="C90">
-        <v>-391.9955352346036</v>
+        <v>-409.206497958623</v>
       </c>
       <c r="D90">
-        <v>553.9204647653964</v>
+        <v>550.116502041377</v>
       </c>
       <c r="E90">
-        <v>600.316</v>
+        <v>613.723</v>
       </c>
       <c r="F90">
-        <v>1179.816</v>
+        <v>1193.223</v>
       </c>
       <c r="G90">
         <v>233.9</v>
@@ -8673,37 +8673,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M90">
-        <v>236.9070528</v>
+        <v>239.5991784</v>
       </c>
       <c r="N90">
-        <v>-98.67371946666668</v>
+        <v>-101.3658450666667</v>
       </c>
       <c r="O90">
-        <v>-20.721481088</v>
+        <v>-21.286827464</v>
       </c>
       <c r="P90">
-        <v>-77.95223837866668</v>
+        <v>-80.07901760266668</v>
       </c>
       <c r="Q90">
-        <v>3.947761621333328</v>
+        <v>1.820982397333324</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4072985162218125</v>
+        <v>0.4401620176965227</v>
       </c>
       <c r="T90">
-        <v>6.095384320079745</v>
+        <v>6.649510167359722</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.122533287451373</v>
+        <v>0.1211565089406834</v>
       </c>
       <c r="W90">
-        <v>0.1761953158797643</v>
+        <v>0.1764717730047108</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5834918450065381</v>
+        <v>0.5769357568603972</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2054776999208101</v>
+        <v>0.2070276999208101</v>
       </c>
       <c r="C91">
-        <v>-409.206497958623</v>
+        <v>-426.3655707825681</v>
       </c>
       <c r="D91">
-        <v>550.116502041377</v>
+        <v>546.3644292174321</v>
       </c>
       <c r="E91">
-        <v>613.723</v>
+        <v>627.1300000000001</v>
       </c>
       <c r="F91">
-        <v>1193.223</v>
+        <v>1206.63</v>
       </c>
       <c r="G91">
         <v>233.9</v>
@@ -8755,37 +8755,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M91">
-        <v>239.5991784</v>
+        <v>242.291304</v>
       </c>
       <c r="N91">
-        <v>-101.3658450666667</v>
+        <v>-104.0579706666667</v>
       </c>
       <c r="O91">
-        <v>-21.286827464</v>
+        <v>-21.85217384000001</v>
       </c>
       <c r="P91">
-        <v>-80.07901760266668</v>
+        <v>-82.2057968266667</v>
       </c>
       <c r="Q91">
-        <v>1.820982397333324</v>
+        <v>-0.3057968266666933</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4401620176965227</v>
+        <v>0.479598219466175</v>
       </c>
       <c r="T91">
-        <v>6.649510167359722</v>
+        <v>7.314461184095694</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1211565089406834</v>
+        <v>0.1198103255080091</v>
       </c>
       <c r="W91">
-        <v>0.1764717730047108</v>
+        <v>0.1767420866379918</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5769357568603972</v>
+        <v>0.5705253595619482</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2070276999208101</v>
+        <v>0.2085776999208101</v>
       </c>
       <c r="C92">
-        <v>-426.3655707825681</v>
+        <v>-443.4738082599523</v>
       </c>
       <c r="D92">
-        <v>546.3644292174321</v>
+        <v>542.6631917400478</v>
       </c>
       <c r="E92">
-        <v>627.1300000000001</v>
+        <v>640.537</v>
       </c>
       <c r="F92">
-        <v>1206.63</v>
+        <v>1220.037</v>
       </c>
       <c r="G92">
         <v>233.9</v>
@@ -8837,37 +8837,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M92">
-        <v>242.291304</v>
+        <v>244.9834296</v>
       </c>
       <c r="N92">
-        <v>-104.0579706666667</v>
+        <v>-106.7500962666667</v>
       </c>
       <c r="O92">
-        <v>-21.85217384000001</v>
+        <v>-22.41752021600001</v>
       </c>
       <c r="P92">
-        <v>-82.2057968266667</v>
+        <v>-84.33257605066669</v>
       </c>
       <c r="Q92">
-        <v>-0.3057968266666933</v>
+        <v>-2.432576050666682</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.479598219466175</v>
+        <v>0.5277980216290834</v>
       </c>
       <c r="T92">
-        <v>7.314461184095694</v>
+        <v>8.127179093439661</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1198103255080091</v>
+        <v>0.1184937285244046</v>
       </c>
       <c r="W92">
-        <v>0.1767420866379918</v>
+        <v>0.1770064593122996</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5705253595619482</v>
+        <v>0.5642558501162125</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2085776999208101</v>
+        <v>0.2101276999208101</v>
       </c>
       <c r="C93">
-        <v>-443.4738082599523</v>
+        <v>-460.5322365611111</v>
       </c>
       <c r="D93">
-        <v>542.6631917400478</v>
+        <v>539.0117634388891</v>
       </c>
       <c r="E93">
-        <v>640.537</v>
+        <v>653.9440000000002</v>
       </c>
       <c r="F93">
-        <v>1220.037</v>
+        <v>1233.444</v>
       </c>
       <c r="G93">
         <v>233.9</v>
@@ -8919,37 +8919,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M93">
-        <v>244.9834296</v>
+        <v>247.6755552</v>
       </c>
       <c r="N93">
-        <v>-106.7500962666667</v>
+        <v>-109.4422218666667</v>
       </c>
       <c r="O93">
-        <v>-22.41752021600001</v>
+        <v>-22.98286659200001</v>
       </c>
       <c r="P93">
-        <v>-84.33257605066669</v>
+        <v>-86.45935527466672</v>
       </c>
       <c r="Q93">
-        <v>-2.432576050666682</v>
+        <v>-4.559355274666714</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5277980216290834</v>
+        <v>0.5880477743327189</v>
       </c>
       <c r="T93">
-        <v>8.127179093439661</v>
+        <v>9.143076480119621</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1184937285244046</v>
+        <v>0.1172057532143567</v>
       </c>
       <c r="W93">
-        <v>0.1770064593122996</v>
+        <v>0.1772650847545572</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5642558501162125</v>
+        <v>0.5581226343540797</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2101276999208101</v>
+        <v>0.2116776999208101</v>
       </c>
       <c r="C94">
-        <v>-460.5322365611111</v>
+        <v>-477.541854421731</v>
       </c>
       <c r="D94">
-        <v>539.0117634388891</v>
+        <v>535.4091455782691</v>
       </c>
       <c r="E94">
-        <v>653.9440000000002</v>
+        <v>667.3510000000001</v>
       </c>
       <c r="F94">
-        <v>1233.444</v>
+        <v>1246.851</v>
       </c>
       <c r="G94">
         <v>233.9</v>
@@ -9001,37 +9001,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M94">
-        <v>247.6755552</v>
+        <v>250.3676808</v>
       </c>
       <c r="N94">
-        <v>-109.4422218666667</v>
+        <v>-112.1343474666667</v>
       </c>
       <c r="O94">
-        <v>-22.98286659200001</v>
+        <v>-23.548212968</v>
       </c>
       <c r="P94">
-        <v>-86.45935527466672</v>
+        <v>-88.58613449866669</v>
       </c>
       <c r="Q94">
-        <v>-4.559355274666714</v>
+        <v>-6.686134498666689</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5880477743327189</v>
+        <v>0.665511742094536</v>
       </c>
       <c r="T94">
-        <v>9.143076480119621</v>
+        <v>10.44923026299385</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1172057532143567</v>
+        <v>0.1159454762980734</v>
       </c>
       <c r="W94">
-        <v>0.1772650847545572</v>
+        <v>0.1775181483593469</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5581226343540797</v>
+        <v>0.5521213157051112</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2116776999208101</v>
+        <v>0.2132276999208101</v>
       </c>
       <c r="C95">
-        <v>-477.541854421731</v>
+        <v>-494.5036340535942</v>
       </c>
       <c r="D95">
-        <v>535.4091455782691</v>
+        <v>531.8543659464059</v>
       </c>
       <c r="E95">
-        <v>667.3510000000001</v>
+        <v>680.758</v>
       </c>
       <c r="F95">
-        <v>1246.851</v>
+        <v>1260.258</v>
       </c>
       <c r="G95">
         <v>233.9</v>
@@ -9083,37 +9083,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M95">
-        <v>250.3676808</v>
+        <v>253.0598064</v>
       </c>
       <c r="N95">
-        <v>-112.1343474666667</v>
+        <v>-114.8264730666667</v>
       </c>
       <c r="O95">
-        <v>-23.548212968</v>
+        <v>-24.11355934400001</v>
       </c>
       <c r="P95">
-        <v>-88.58613449866669</v>
+        <v>-90.71291372266668</v>
       </c>
       <c r="Q95">
-        <v>-6.686134498666689</v>
+        <v>-8.812913722666678</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.665511742094536</v>
+        <v>0.7687970324436255</v>
       </c>
       <c r="T95">
-        <v>10.44923026299385</v>
+        <v>12.1907686401595</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1159454762980734</v>
+        <v>0.1147120137842641</v>
       </c>
       <c r="W95">
-        <v>0.1775181483593469</v>
+        <v>0.1777658276321198</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5521213157051112</v>
+        <v>0.5462476846869717</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2132276999208101</v>
+        <v>0.2147776999208101</v>
       </c>
       <c r="C96">
-        <v>-494.5036340535942</v>
+        <v>-511.4185220192809</v>
       </c>
       <c r="D96">
-        <v>531.8543659464059</v>
+        <v>528.3464779807193</v>
       </c>
       <c r="E96">
-        <v>680.758</v>
+        <v>694.1650000000002</v>
       </c>
       <c r="F96">
-        <v>1260.258</v>
+        <v>1273.665</v>
       </c>
       <c r="G96">
         <v>233.9</v>
@@ -9165,37 +9165,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M96">
-        <v>253.0598064</v>
+        <v>255.751932</v>
       </c>
       <c r="N96">
-        <v>-114.8264730666667</v>
+        <v>-117.5185986666667</v>
       </c>
       <c r="O96">
-        <v>-24.11355934400001</v>
+        <v>-24.67890572000001</v>
       </c>
       <c r="P96">
-        <v>-90.71291372266668</v>
+        <v>-92.8396929466667</v>
       </c>
       <c r="Q96">
-        <v>-8.812913722666678</v>
+        <v>-10.9396929466667</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7687970324436255</v>
+        <v>0.9133964389323511</v>
       </c>
       <c r="T96">
-        <v>12.1907686401595</v>
+        <v>14.62892236819141</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1147120137842641</v>
+        <v>0.1135045189023244</v>
       </c>
       <c r="W96">
-        <v>0.1777658276321198</v>
+        <v>0.1780082926044133</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5462476846869717</v>
+        <v>0.5404977090586878</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2147776999208101</v>
+        <v>0.2163276999208101</v>
       </c>
       <c r="C97">
-        <v>-511.4185220192809</v>
+        <v>-528.2874400724832</v>
       </c>
       <c r="D97">
-        <v>528.3464779807193</v>
+        <v>524.884559927517</v>
       </c>
       <c r="E97">
-        <v>694.1650000000002</v>
+        <v>707.5720000000001</v>
       </c>
       <c r="F97">
-        <v>1273.665</v>
+        <v>1287.072</v>
       </c>
       <c r="G97">
         <v>233.9</v>
@@ -9247,37 +9247,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M97">
-        <v>255.751932</v>
+        <v>258.4440576</v>
       </c>
       <c r="N97">
-        <v>-117.5185986666667</v>
+        <v>-120.2107242666667</v>
       </c>
       <c r="O97">
-        <v>-24.67890572000001</v>
+        <v>-25.244252096</v>
       </c>
       <c r="P97">
-        <v>-92.8396929466667</v>
+        <v>-94.96647217066669</v>
       </c>
       <c r="Q97">
-        <v>-10.9396929466667</v>
+        <v>-13.06647217066669</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9133964389323511</v>
+        <v>1.130295548665439</v>
       </c>
       <c r="T97">
-        <v>14.62892236819141</v>
+        <v>18.28615296023926</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1135045189023244</v>
+        <v>0.1123221801637586</v>
       </c>
       <c r="W97">
-        <v>0.1780082926044133</v>
+        <v>0.1782457062231173</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5404977090586878</v>
+        <v>0.5348675245893265</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2163276999208101</v>
+        <v>0.2178776999208101</v>
       </c>
       <c r="C98">
-        <v>-528.2874400724829</v>
+        <v>-545.1112859654997</v>
       </c>
       <c r="D98">
-        <v>524.884559927517</v>
+        <v>521.4677140345003</v>
       </c>
       <c r="E98">
-        <v>707.5719999999999</v>
+        <v>720.979</v>
       </c>
       <c r="F98">
-        <v>1287.072</v>
+        <v>1300.479</v>
       </c>
       <c r="G98">
         <v>233.9</v>
@@ -9329,37 +9329,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M98">
-        <v>258.4440576</v>
+        <v>261.1361832</v>
       </c>
       <c r="N98">
-        <v>-120.2107242666667</v>
+        <v>-122.9028498666667</v>
       </c>
       <c r="O98">
-        <v>-25.244252096</v>
+        <v>-25.809598472</v>
       </c>
       <c r="P98">
-        <v>-94.96647217066669</v>
+        <v>-97.09325139466668</v>
       </c>
       <c r="Q98">
-        <v>-13.06647217066669</v>
+        <v>-15.19325139466667</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.130295548665436</v>
+        <v>1.491794064887249</v>
       </c>
       <c r="T98">
-        <v>18.28615296023921</v>
+        <v>24.38153728031896</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1123221801637586</v>
+        <v>0.1111642195435136</v>
       </c>
       <c r="W98">
-        <v>0.1782457062231173</v>
+        <v>0.1784782247156625</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5348675245893265</v>
+        <v>0.529353426397684</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2178776999208101</v>
+        <v>0.2194276999208101</v>
       </c>
       <c r="C99">
-        <v>-545.1112859654997</v>
+        <v>-561.8909342253925</v>
       </c>
       <c r="D99">
-        <v>521.4677140345003</v>
+        <v>518.0950657746075</v>
       </c>
       <c r="E99">
-        <v>720.979</v>
+        <v>734.386</v>
       </c>
       <c r="F99">
-        <v>1300.479</v>
+        <v>1313.886</v>
       </c>
       <c r="G99">
         <v>233.9</v>
@@ -9411,37 +9411,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M99">
-        <v>261.1361832</v>
+        <v>263.8283088</v>
       </c>
       <c r="N99">
-        <v>-122.9028498666667</v>
+        <v>-125.5949754666667</v>
       </c>
       <c r="O99">
-        <v>-25.809598472</v>
+        <v>-26.374944848</v>
       </c>
       <c r="P99">
-        <v>-97.09325139466668</v>
+        <v>-99.22003061866668</v>
       </c>
       <c r="Q99">
-        <v>-15.19325139466667</v>
+        <v>-17.32003061866668</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.491794064887249</v>
+        <v>2.214791097330873</v>
       </c>
       <c r="T99">
-        <v>24.38153728031896</v>
+        <v>36.57230592047843</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1111642195435136</v>
+        <v>0.1100298907726614</v>
       </c>
       <c r="W99">
-        <v>0.1784782247156625</v>
+        <v>0.1787059979328496</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.529353426397684</v>
+        <v>0.5239518608221974</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2194276999208101</v>
+        <v>0.2209776999208101</v>
       </c>
       <c r="C100">
-        <v>-561.8909342253925</v>
+        <v>-578.6272369002194</v>
       </c>
       <c r="D100">
-        <v>518.0950657746075</v>
+        <v>514.7657630997808</v>
       </c>
       <c r="E100">
-        <v>734.386</v>
+        <v>747.7930000000001</v>
       </c>
       <c r="F100">
-        <v>1313.886</v>
+        <v>1327.293</v>
       </c>
       <c r="G100">
         <v>233.9</v>
@@ -9493,37 +9493,37 @@
         <v>138.2333333333333</v>
       </c>
       <c r="M100">
-        <v>263.8283088</v>
+        <v>266.5204344000001</v>
       </c>
       <c r="N100">
-        <v>-125.5949754666667</v>
+        <v>-128.2871010666667</v>
       </c>
       <c r="O100">
-        <v>-26.374944848</v>
+        <v>-26.94029122400001</v>
       </c>
       <c r="P100">
-        <v>-99.22003061866668</v>
+        <v>-101.3468098426667</v>
       </c>
       <c r="Q100">
-        <v>-17.32003061866668</v>
+        <v>-19.44680984266671</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.214791097330873</v>
+        <v>4.383782194661745</v>
       </c>
       <c r="T100">
-        <v>36.57230592047843</v>
+        <v>73.14461184095686</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1100298907726614</v>
+        <v>0.1089184777345537</v>
       </c>
       <c r="W100">
-        <v>0.1787059979328496</v>
+        <v>0.1789291696709016</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5239518608221974</v>
+        <v>0.5186594177835893</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2209776999208101</v>
-      </c>
-      <c r="C101">
-        <v>-578.6272369002194</v>
-      </c>
-      <c r="D101">
-        <v>514.7657630997808</v>
-      </c>
-      <c r="E101">
-        <v>747.7930000000001</v>
-      </c>
-      <c r="F101">
-        <v>1327.293</v>
-      </c>
-      <c r="G101">
-        <v>233.9</v>
-      </c>
-      <c r="H101">
-        <v>761.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>220.1333333333333</v>
-      </c>
-      <c r="K101">
-        <v>81.90000000000001</v>
-      </c>
-      <c r="L101">
-        <v>138.2333333333333</v>
-      </c>
-      <c r="M101">
-        <v>266.5204344000001</v>
-      </c>
-      <c r="N101">
-        <v>-128.2871010666667</v>
-      </c>
-      <c r="O101">
-        <v>-26.94029122400001</v>
-      </c>
-      <c r="P101">
-        <v>-101.3468098426667</v>
-      </c>
-      <c r="Q101">
-        <v>-19.44680984266671</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.383782194661745</v>
-      </c>
-      <c r="T101">
-        <v>73.14461184095686</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1089184777345537</v>
-      </c>
-      <c r="W101">
-        <v>0.1789291696709016</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5186594177835893</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
